--- a/poker/resources/sample/dropGroup.xlsx
+++ b/poker/resources/sample/dropGroup.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -98,6 +98,9 @@
     <t>子包组</t>
   </si>
   <si>
+    <t>每天掉落次数</t>
+  </si>
+  <si>
     <t>子包1</t>
   </si>
   <si>
@@ -126,6 +129,9 @@
   </si>
   <si>
     <t>dropDetailedID</t>
+  </si>
+  <si>
+    <t>dropCount</t>
   </si>
   <si>
     <t>随机金币礼包</t>
@@ -1180,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -1188,15 +1194,16 @@
     <col min="3" max="3" width="9.375" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
     <col min="5" max="5" width="28.25" customWidth="1"/>
-    <col min="6" max="6" width="13.75" customWidth="1"/>
-    <col min="8" max="8" width="9.375"/>
-    <col min="9" max="9" width="19.875" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="12" max="12" width="9.375"/>
-    <col min="13" max="13" width="23.25" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="9" max="9" width="9.375"/>
+    <col min="10" max="10" width="19.875" customWidth="1"/>
+    <col min="11" max="11" width="13.75" customWidth="1"/>
+    <col min="13" max="13" width="9.375"/>
+    <col min="14" max="14" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L1" t="s">
         <v>6</v>
@@ -1233,35 +1240,44 @@
       <c r="M1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="N1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>10000101</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>100001</v>
@@ -1270,39 +1286,42 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>100</v>
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
       </c>
       <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
         <v>20000000</v>
       </c>
-      <c r="I5" t="s">
-        <v>17</v>
-      </c>
       <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5">
+        <v>19</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5">
         <v>900</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>20000001</v>
       </c>
-      <c r="M5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>10000102</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>100001</v>
@@ -1311,39 +1330,42 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>100</v>
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
       </c>
       <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
         <v>20000000</v>
       </c>
-      <c r="I6" t="s">
-        <v>17</v>
-      </c>
       <c r="J6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6">
         <v>900</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>20000002</v>
       </c>
-      <c r="M6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>10000103</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>100001</v>
@@ -1352,39 +1374,42 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
       </c>
       <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
         <v>20000000</v>
       </c>
-      <c r="I7" t="s">
-        <v>17</v>
-      </c>
       <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7">
+        <v>19</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7">
         <v>900</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>20000003</v>
       </c>
-      <c r="M7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>10000104</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>100001</v>
@@ -1393,39 +1418,42 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>100</v>
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
       </c>
       <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
         <v>20000000</v>
       </c>
-      <c r="I8" t="s">
-        <v>17</v>
-      </c>
       <c r="J8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8">
+        <v>19</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8">
         <v>900</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>20000004</v>
       </c>
-      <c r="M8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>10000201</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>100002</v>
@@ -1434,39 +1462,42 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9">
+        <v>500</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>500</v>
+      </c>
+      <c r="M9">
+        <v>20000004</v>
+      </c>
+      <c r="N9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9">
-        <v>500</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9">
-        <v>500</v>
-      </c>
-      <c r="L9">
-        <v>20000004</v>
-      </c>
-      <c r="M9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:5">
+    </row>
+    <row r="10" customFormat="1" spans="1:6">
       <c r="A10">
         <v>10000301</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>100003</v>
@@ -1475,15 +1506,18 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:5">
+        <v>37</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:6">
       <c r="A11">
         <v>10000302</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>100003</v>
@@ -1492,15 +1526,18 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:5">
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:6">
       <c r="A12">
         <v>10000303</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>100003</v>
@@ -1509,15 +1546,18 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:5">
+        <v>37</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:6">
       <c r="A13">
         <v>10000401</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>100004</v>
@@ -1526,15 +1566,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:5">
+        <v>39</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:6">
       <c r="A14">
         <v>10000402</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>100004</v>
@@ -1543,15 +1586,18 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:5">
+        <v>39</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:6">
       <c r="A15">
         <v>10000403</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>100004</v>
@@ -1560,15 +1606,18 @@
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:5">
+        <v>39</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:6">
       <c r="A16">
         <v>10000501</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>100005</v>
@@ -1577,15 +1626,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:5">
+        <v>41</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:6">
       <c r="A17">
         <v>10000502</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>100005</v>
@@ -1594,15 +1646,18 @@
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:5">
+        <v>41</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:6">
       <c r="A18">
         <v>10000503</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>100005</v>
@@ -1611,15 +1666,18 @@
         <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>41</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>10000601</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>100006</v>
@@ -1628,15 +1686,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>43</v>
+      </c>
+      <c r="F19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>10000602</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>100006</v>
@@ -1645,15 +1706,18 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>43</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>10000603</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>100006</v>
@@ -1662,15 +1726,18 @@
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>43</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>10000611</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>100007</v>
@@ -1679,15 +1746,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>45</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>10000612</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>100007</v>
@@ -1696,15 +1766,18 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>45</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>10000613</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C24">
         <v>100007</v>
@@ -1713,15 +1786,18 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>45</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>10000621</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>100008</v>
@@ -1730,15 +1806,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>47</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>10000622</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>100008</v>
@@ -1747,15 +1826,18 @@
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>47</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>10000623</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C27">
         <v>100008</v>
@@ -1764,15 +1846,18 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:5">
+        <v>47</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:6">
       <c r="A28">
         <v>10000631</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>100009</v>
@@ -1781,15 +1866,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:5">
+        <v>49</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:6">
       <c r="A29">
         <v>10000632</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C29">
         <v>100009</v>
@@ -1798,15 +1886,18 @@
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:5">
+        <v>49</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:6">
       <c r="A30">
         <v>10000633</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C30">
         <v>100009</v>
@@ -1815,15 +1906,18 @@
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:5">
+        <v>49</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:6">
       <c r="A31">
         <v>10000641</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>100010</v>
@@ -1832,15 +1926,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:5">
+        <v>51</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:6">
       <c r="A32">
         <v>10000642</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C32">
         <v>100010</v>
@@ -1849,15 +1946,18 @@
         <v>2</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:5">
+        <v>51</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
       <c r="A33">
         <v>10000643</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C33">
         <v>100010</v>
@@ -1866,15 +1966,18 @@
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>51</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>10000651</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C34">
         <v>100011</v>
@@ -1883,7 +1986,10 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/dropGroup.xlsx
+++ b/poker/resources/sample/dropGroup.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -243,6 +243,42 @@
   </si>
   <si>
     <t>500_20000021|500_0</t>
+  </si>
+  <si>
+    <t>赌场材料-40级</t>
+  </si>
+  <si>
+    <t>赌场材料-50级</t>
+  </si>
+  <si>
+    <t>赌场材料-60级</t>
+  </si>
+  <si>
+    <t>赌场材料-70级</t>
+  </si>
+  <si>
+    <t>赌场材料-80级</t>
+  </si>
+  <si>
+    <t>赌场材料-90级</t>
+  </si>
+  <si>
+    <t>赌场材料-100级</t>
+  </si>
+  <si>
+    <t>赌场材料-110级</t>
+  </si>
+  <si>
+    <t>赌场材料-120级</t>
+  </si>
+  <si>
+    <t>赌场材料-130级</t>
+  </si>
+  <si>
+    <t>赌场材料-140级</t>
+  </si>
+  <si>
+    <t>赌场材料-150级</t>
   </si>
 </sst>
 </file>
@@ -419,12 +455,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -745,7 +787,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -769,16 +811,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -787,91 +829,94 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1186,7 +1231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -1992,6 +2037,546 @@
         <v>100</v>
       </c>
     </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="1">
+        <v>10010040</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35">
+        <v>10040</v>
+      </c>
+      <c r="E35" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G35,K35)</f>
+        <v>7250_0|2750_20010040</v>
+      </c>
+      <c r="F35">
+        <v>99999</v>
+      </c>
+      <c r="G35" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H35:I35)</f>
+        <v>7250_0</v>
+      </c>
+      <c r="H35">
+        <v>7250</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L35:M35)</f>
+        <v>2750_20010040</v>
+      </c>
+      <c r="L35">
+        <f>10000-H35</f>
+        <v>2750</v>
+      </c>
+      <c r="M35">
+        <v>20010040</v>
+      </c>
+      <c r="N35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="1">
+        <v>10010050</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36">
+        <v>10050</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" ref="E36:E46" si="0">_xlfn.TEXTJOIN("|",TRUE,G36,K36)</f>
+        <v>7226_0|2774_20010050</v>
+      </c>
+      <c r="F36">
+        <v>99999</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" ref="G36:G46" si="1">_xlfn.TEXTJOIN("_",TRUE,H36:I36)</f>
+        <v>7226_0</v>
+      </c>
+      <c r="H36">
+        <v>7226</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" t="str">
+        <f t="shared" ref="K36:K46" si="2">_xlfn.TEXTJOIN("_",TRUE,L36:M36)</f>
+        <v>2774_20010050</v>
+      </c>
+      <c r="L36">
+        <f t="shared" ref="L36:L46" si="3">10000-H36</f>
+        <v>2774</v>
+      </c>
+      <c r="M36">
+        <v>20010050</v>
+      </c>
+      <c r="N36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="1">
+        <v>10010060</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37">
+        <v>10060</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="0"/>
+        <v>6588_0|3412_20010060</v>
+      </c>
+      <c r="F37">
+        <v>99999</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="1"/>
+        <v>6588_0</v>
+      </c>
+      <c r="H37">
+        <v>6588</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K37" t="str">
+        <f t="shared" si="2"/>
+        <v>3412_20010060</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="3"/>
+        <v>3412</v>
+      </c>
+      <c r="M37">
+        <v>20010060</v>
+      </c>
+      <c r="N37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="1">
+        <v>10010070</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38">
+        <v>10070</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="0"/>
+        <v>7788_0|2212_20010070</v>
+      </c>
+      <c r="F38">
+        <v>99999</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="1"/>
+        <v>7788_0</v>
+      </c>
+      <c r="H38">
+        <v>7788</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38" t="s">
+        <v>34</v>
+      </c>
+      <c r="K38" t="str">
+        <f t="shared" si="2"/>
+        <v>2212_20010070</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="3"/>
+        <v>2212</v>
+      </c>
+      <c r="M38">
+        <v>20010070</v>
+      </c>
+      <c r="N38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="1">
+        <v>10010080</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39">
+        <v>10080</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="0"/>
+        <v>6951_0|3049_20010080</v>
+      </c>
+      <c r="F39">
+        <v>99999</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" si="1"/>
+        <v>6951_0</v>
+      </c>
+      <c r="H39">
+        <v>6951</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" t="str">
+        <f t="shared" si="2"/>
+        <v>3049_20010080</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="3"/>
+        <v>3049</v>
+      </c>
+      <c r="M39">
+        <v>20010080</v>
+      </c>
+      <c r="N39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="1">
+        <v>10010090</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40">
+        <v>10090</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" si="0"/>
+        <v>7861_0|2139_20010090</v>
+      </c>
+      <c r="F40">
+        <v>99999</v>
+      </c>
+      <c r="G40" t="str">
+        <f t="shared" si="1"/>
+        <v>7861_0</v>
+      </c>
+      <c r="H40">
+        <v>7861</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" t="str">
+        <f t="shared" si="2"/>
+        <v>2139_20010090</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="3"/>
+        <v>2139</v>
+      </c>
+      <c r="M40">
+        <v>20010090</v>
+      </c>
+      <c r="N40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="1">
+        <v>10010100</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41">
+        <v>10100</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="0"/>
+        <v>7826_0|2174_20010100</v>
+      </c>
+      <c r="F41">
+        <v>99999</v>
+      </c>
+      <c r="G41" t="str">
+        <f t="shared" si="1"/>
+        <v>7826_0</v>
+      </c>
+      <c r="H41">
+        <v>7826</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41" t="s">
+        <v>34</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" si="2"/>
+        <v>2174_20010100</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="3"/>
+        <v>2174</v>
+      </c>
+      <c r="M41">
+        <v>20010100</v>
+      </c>
+      <c r="N41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="1">
+        <v>10010110</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42">
+        <v>10110</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="0"/>
+        <v>7858_0|2142_20010110</v>
+      </c>
+      <c r="F42">
+        <v>99999</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="1"/>
+        <v>7858_0</v>
+      </c>
+      <c r="H42">
+        <v>7858</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" t="s">
+        <v>34</v>
+      </c>
+      <c r="K42" t="str">
+        <f t="shared" si="2"/>
+        <v>2142_20010110</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="3"/>
+        <v>2142</v>
+      </c>
+      <c r="M42">
+        <v>20010110</v>
+      </c>
+      <c r="N42" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="1">
+        <v>10010120</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43">
+        <v>10120</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="0"/>
+        <v>7779_0|2221_20010120</v>
+      </c>
+      <c r="F43">
+        <v>99999</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="1"/>
+        <v>7779_0</v>
+      </c>
+      <c r="H43">
+        <v>7779</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" t="s">
+        <v>34</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="2"/>
+        <v>2221_20010120</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="3"/>
+        <v>2221</v>
+      </c>
+      <c r="M43">
+        <v>20010120</v>
+      </c>
+      <c r="N43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="1">
+        <v>10010130</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44">
+        <v>10130</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="0"/>
+        <v>7828_0|2172_20010130</v>
+      </c>
+      <c r="F44">
+        <v>99999</v>
+      </c>
+      <c r="G44" t="str">
+        <f t="shared" si="1"/>
+        <v>7828_0</v>
+      </c>
+      <c r="H44">
+        <v>7828</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>34</v>
+      </c>
+      <c r="K44" t="str">
+        <f t="shared" si="2"/>
+        <v>2172_20010130</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="3"/>
+        <v>2172</v>
+      </c>
+      <c r="M44">
+        <v>20010130</v>
+      </c>
+      <c r="N44" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="1">
+        <v>10010140</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45">
+        <v>10140</v>
+      </c>
+      <c r="E45" t="str">
+        <f t="shared" si="0"/>
+        <v>8677_0|1323_20010140</v>
+      </c>
+      <c r="F45">
+        <v>99999</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" si="1"/>
+        <v>8677_0</v>
+      </c>
+      <c r="H45">
+        <v>8677</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" t="str">
+        <f t="shared" si="2"/>
+        <v>1323_20010140</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="3"/>
+        <v>1323</v>
+      </c>
+      <c r="M45">
+        <v>20010140</v>
+      </c>
+      <c r="N45" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="1">
+        <v>10010150</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46">
+        <v>10150</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="0"/>
+        <v>8981_0|1019_20010150</v>
+      </c>
+      <c r="F46">
+        <v>99999</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="1"/>
+        <v>8981_0</v>
+      </c>
+      <c r="H46">
+        <v>8981</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K46" t="str">
+        <f t="shared" si="2"/>
+        <v>1019_20010150</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="3"/>
+        <v>1019</v>
+      </c>
+      <c r="M46">
+        <v>20010150</v>
+      </c>
+      <c r="N46" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/dropGroup.xlsx
+++ b/poker/resources/sample/dropGroup.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -194,24 +194,6 @@
     <t>500_20000004</t>
   </si>
   <si>
-    <t>赌场材料包(普通)</t>
-  </si>
-  <si>
-    <t>1000_20000005</t>
-  </si>
-  <si>
-    <t>赌场材料包(豪华)</t>
-  </si>
-  <si>
-    <t>1000_20000006</t>
-  </si>
-  <si>
-    <t>赌场材料包(尊贵)</t>
-  </si>
-  <si>
-    <t>1000_20000007</t>
-  </si>
-  <si>
     <t>拼图碎片包1</t>
   </si>
   <si>
@@ -279,6 +261,45 @@
   </si>
   <si>
     <t>赌场材料-150级</t>
+  </si>
+  <si>
+    <t>赌场工具（普通）</t>
+  </si>
+  <si>
+    <t>1星材料包</t>
+  </si>
+  <si>
+    <t>2星材料包</t>
+  </si>
+  <si>
+    <t>赌场工具（精良）</t>
+  </si>
+  <si>
+    <t>1星材料包X2</t>
+  </si>
+  <si>
+    <t>赌场工具（优秀）</t>
+  </si>
+  <si>
+    <t>2星材料包X2</t>
+  </si>
+  <si>
+    <t>3星材料包</t>
+  </si>
+  <si>
+    <t>赌场工具（绝佳）</t>
+  </si>
+  <si>
+    <t>4星材料包</t>
+  </si>
+  <si>
+    <t>赌场工具（传奇）</t>
+  </si>
+  <si>
+    <t>3星材料包X2</t>
+  </si>
+  <si>
+    <t>5星材料包</t>
   </si>
 </sst>
 </file>
@@ -291,10 +312,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -455,7 +482,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,6 +492,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -781,142 +850,166 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1231,10 +1324,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.375"/>
+    <col min="1" max="1" width="10.375"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
     <col min="3" max="3" width="9.375" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
@@ -1537,15 +1630,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:6">
+    <row r="10" spans="1:6">
       <c r="A10">
-        <v>10000301</v>
+        <v>10000601</v>
       </c>
       <c r="B10" t="s">
         <v>36</v>
       </c>
       <c r="C10">
-        <v>100003</v>
+        <v>100006</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1557,15 +1650,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:6">
+    <row r="11" spans="1:6">
       <c r="A11">
-        <v>10000302</v>
+        <v>10000602</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
       </c>
       <c r="C11">
-        <v>100003</v>
+        <v>100006</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1577,15 +1670,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:6">
+    <row r="12" spans="1:6">
       <c r="A12">
-        <v>10000303</v>
+        <v>10000603</v>
       </c>
       <c r="B12" t="s">
         <v>36</v>
       </c>
       <c r="C12">
-        <v>100003</v>
+        <v>100006</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -1597,15 +1690,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:6">
+    <row r="13" spans="1:6">
       <c r="A13">
-        <v>10000401</v>
+        <v>10000611</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
       </c>
       <c r="C13">
-        <v>100004</v>
+        <v>100007</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1617,15 +1710,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:6">
+    <row r="14" spans="1:6">
       <c r="A14">
-        <v>10000402</v>
+        <v>10000612</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
       </c>
       <c r="C14">
-        <v>100004</v>
+        <v>100007</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -1637,15 +1730,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:6">
+    <row r="15" spans="1:6">
       <c r="A15">
-        <v>10000403</v>
+        <v>10000613</v>
       </c>
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15">
-        <v>100004</v>
+        <v>100007</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -1657,15 +1750,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:6">
+    <row r="16" spans="1:6">
       <c r="A16">
-        <v>10000501</v>
+        <v>10000621</v>
       </c>
       <c r="B16" t="s">
         <v>40</v>
       </c>
       <c r="C16">
-        <v>100005</v>
+        <v>100008</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1677,15 +1770,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:6">
+    <row r="17" spans="1:6">
       <c r="A17">
-        <v>10000502</v>
+        <v>10000622</v>
       </c>
       <c r="B17" t="s">
         <v>40</v>
       </c>
       <c r="C17">
-        <v>100005</v>
+        <v>100008</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1697,15 +1790,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:6">
+    <row r="18" spans="1:6">
       <c r="A18">
-        <v>10000503</v>
+        <v>10000623</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
       </c>
       <c r="C18">
-        <v>100005</v>
+        <v>100008</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1717,15 +1810,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" customFormat="1" spans="1:6">
       <c r="A19">
-        <v>10000601</v>
+        <v>10000631</v>
       </c>
       <c r="B19" t="s">
         <v>42</v>
       </c>
       <c r="C19">
-        <v>100006</v>
+        <v>100009</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1737,15 +1830,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" customFormat="1" spans="1:6">
       <c r="A20">
-        <v>10000602</v>
+        <v>10000632</v>
       </c>
       <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20">
-        <v>100006</v>
+        <v>100009</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1757,15 +1850,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" customFormat="1" spans="1:6">
       <c r="A21">
-        <v>10000603</v>
+        <v>10000633</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21">
-        <v>100006</v>
+        <v>100009</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1777,15 +1870,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" customFormat="1" spans="1:6">
       <c r="A22">
-        <v>10000611</v>
+        <v>10000641</v>
       </c>
       <c r="B22" t="s">
         <v>44</v>
       </c>
       <c r="C22">
-        <v>100007</v>
+        <v>100010</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1797,15 +1890,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" customFormat="1" spans="1:6">
       <c r="A23">
-        <v>10000612</v>
+        <v>10000642</v>
       </c>
       <c r="B23" t="s">
         <v>44</v>
       </c>
       <c r="C23">
-        <v>100007</v>
+        <v>100010</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1817,15 +1910,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" customFormat="1" spans="1:6">
       <c r="A24">
-        <v>10000613</v>
+        <v>10000643</v>
       </c>
       <c r="B24" t="s">
         <v>44</v>
       </c>
       <c r="C24">
-        <v>100007</v>
+        <v>100010</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1839,227 +1932,452 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>10000621</v>
+        <v>10000651</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C25">
-        <v>100008</v>
+        <v>100011</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>10000622</v>
-      </c>
-      <c r="B26" t="s">
-        <v>46</v>
+    <row r="26" spans="1:14">
+      <c r="A26" s="1">
+        <v>10010040</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C26">
-        <v>100008</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26" t="s">
+        <v>10040</v>
+      </c>
+      <c r="E26" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G26,K26)</f>
+        <v>7250_0|2750_20010040</v>
+      </c>
+      <c r="F26">
+        <v>99999</v>
+      </c>
+      <c r="G26" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H26:I26)</f>
+        <v>7250_0</v>
+      </c>
+      <c r="H26">
+        <v>7250</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L26:M26)</f>
+        <v>2750_20010040</v>
+      </c>
+      <c r="L26">
+        <f>10000-H26</f>
+        <v>2750</v>
+      </c>
+      <c r="M26">
+        <v>20010040</v>
+      </c>
+      <c r="N26" t="s">
         <v>47</v>
       </c>
-      <c r="F26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>10000623</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="1">
+        <v>10010050</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C27">
-        <v>100008</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>47</v>
+        <v>10050</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" ref="E27:E43" si="0">_xlfn.TEXTJOIN("|",TRUE,G27,K27)</f>
+        <v>7226_0|2774_20010050</v>
       </c>
       <c r="F27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:6">
-      <c r="A28">
-        <v>10000631</v>
-      </c>
-      <c r="B28" t="s">
+        <v>99999</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" ref="G27:G43" si="1">_xlfn.TEXTJOIN("_",TRUE,H27:I27)</f>
+        <v>7226_0</v>
+      </c>
+      <c r="H27">
+        <v>7226</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" t="str">
+        <f t="shared" ref="K27:K37" si="2">_xlfn.TEXTJOIN("_",TRUE,L27:M27)</f>
+        <v>2774_20010050</v>
+      </c>
+      <c r="L27">
+        <f t="shared" ref="L27:L37" si="3">10000-H27</f>
+        <v>2774</v>
+      </c>
+      <c r="M27">
+        <v>20010050</v>
+      </c>
+      <c r="N27" t="s">
         <v>48</v>
       </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="1">
+        <v>10010060</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C28">
-        <v>100009</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
+        <v>10060</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v>6588_0|3412_20010060</v>
+      </c>
+      <c r="F28">
+        <v>99999</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="1"/>
+        <v>6588_0</v>
+      </c>
+      <c r="H28">
+        <v>6588</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" t="str">
+        <f t="shared" si="2"/>
+        <v>3412_20010060</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="3"/>
+        <v>3412</v>
+      </c>
+      <c r="M28">
+        <v>20010060</v>
+      </c>
+      <c r="N28" t="s">
         <v>49</v>
       </c>
-      <c r="F28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:6">
-      <c r="A29">
-        <v>10000632</v>
-      </c>
-      <c r="B29" t="s">
-        <v>48</v>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="1">
+        <v>10010070</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C29">
-        <v>100009</v>
-      </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29" t="s">
-        <v>49</v>
+        <v>10070</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="0"/>
+        <v>7788_0|2212_20010070</v>
       </c>
       <c r="F29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:6">
-      <c r="A30">
-        <v>10000633</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
+        <v>99999</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="1"/>
+        <v>7788_0</v>
+      </c>
+      <c r="H29">
+        <v>7788</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" t="str">
+        <f t="shared" si="2"/>
+        <v>2212_20010070</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="3"/>
+        <v>2212</v>
+      </c>
+      <c r="M29">
+        <v>20010070</v>
+      </c>
+      <c r="N29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="1">
+        <v>10010080</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="C30">
-        <v>100009</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>49</v>
+        <v>10080</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="0"/>
+        <v>6951_0|3049_20010080</v>
       </c>
       <c r="F30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:6">
-      <c r="A31">
-        <v>10000641</v>
-      </c>
-      <c r="B31" t="s">
-        <v>50</v>
+        <v>99999</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="1"/>
+        <v>6951_0</v>
+      </c>
+      <c r="H30">
+        <v>6951</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" t="str">
+        <f t="shared" si="2"/>
+        <v>3049_20010080</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="3"/>
+        <v>3049</v>
+      </c>
+      <c r="M30">
+        <v>20010080</v>
+      </c>
+      <c r="N30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="1">
+        <v>10010090</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C31">
-        <v>100010</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>51</v>
+        <v>10090</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="0"/>
+        <v>7861_0|2139_20010090</v>
       </c>
       <c r="F31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:6">
-      <c r="A32">
-        <v>10000642</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
+        <v>99999</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="1"/>
+        <v>7861_0</v>
+      </c>
+      <c r="H31">
+        <v>7861</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" t="str">
+        <f t="shared" si="2"/>
+        <v>2139_20010090</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="3"/>
+        <v>2139</v>
+      </c>
+      <c r="M31">
+        <v>20010090</v>
+      </c>
+      <c r="N31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="1">
+        <v>10010100</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C32">
-        <v>100010</v>
-      </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-      <c r="E32" t="s">
-        <v>51</v>
+        <v>10100</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="0"/>
+        <v>7826_0|2174_20010100</v>
       </c>
       <c r="F32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:6">
-      <c r="A33">
-        <v>10000643</v>
-      </c>
-      <c r="B33" t="s">
-        <v>50</v>
+        <v>99999</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="1"/>
+        <v>7826_0</v>
+      </c>
+      <c r="H32">
+        <v>7826</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" t="str">
+        <f t="shared" si="2"/>
+        <v>2174_20010100</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="3"/>
+        <v>2174</v>
+      </c>
+      <c r="M32">
+        <v>20010100</v>
+      </c>
+      <c r="N32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="1">
+        <v>10010110</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C33">
-        <v>100010</v>
-      </c>
-      <c r="D33">
-        <v>3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>51</v>
+        <v>10110</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="0"/>
+        <v>7858_0|2142_20010110</v>
       </c>
       <c r="F33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>10000651</v>
-      </c>
-      <c r="B34" t="s">
-        <v>31</v>
+        <v>99999</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="1"/>
+        <v>7858_0</v>
+      </c>
+      <c r="H33">
+        <v>7858</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" t="str">
+        <f t="shared" si="2"/>
+        <v>2142_20010110</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="3"/>
+        <v>2142</v>
+      </c>
+      <c r="M33">
+        <v>20010110</v>
+      </c>
+      <c r="N33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="1">
+        <v>10010120</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C34">
-        <v>100011</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>52</v>
+        <v>10120</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="0"/>
+        <v>7779_0|2221_20010120</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>99999</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="1"/>
+        <v>7779_0</v>
+      </c>
+      <c r="H34">
+        <v>7779</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" t="str">
+        <f t="shared" si="2"/>
+        <v>2221_20010120</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="3"/>
+        <v>2221</v>
+      </c>
+      <c r="M34">
+        <v>20010120</v>
+      </c>
+      <c r="N34" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1">
-        <v>10010040</v>
+        <v>10010130</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C35">
-        <v>10040</v>
+        <v>10130</v>
       </c>
       <c r="E35" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G35,K35)</f>
-        <v>7250_0|2750_20010040</v>
+        <f t="shared" si="0"/>
+        <v>7828_0|2172_20010130</v>
       </c>
       <c r="F35">
         <v>99999</v>
       </c>
       <c r="G35" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H35:I35)</f>
-        <v>7250_0</v>
+        <f t="shared" si="1"/>
+        <v>7828_0</v>
       </c>
       <c r="H35">
-        <v>7250</v>
+        <v>7828</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2068,43 +2386,43 @@
         <v>34</v>
       </c>
       <c r="K35" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L35:M35)</f>
-        <v>2750_20010040</v>
+        <f t="shared" si="2"/>
+        <v>2172_20010130</v>
       </c>
       <c r="L35">
-        <f>10000-H35</f>
-        <v>2750</v>
+        <f t="shared" si="3"/>
+        <v>2172</v>
       </c>
       <c r="M35">
-        <v>20010040</v>
+        <v>20010130</v>
       </c>
       <c r="N35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="1">
-        <v>10010050</v>
+        <v>10010140</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C36">
-        <v>10050</v>
+        <v>10140</v>
       </c>
       <c r="E36" t="str">
-        <f t="shared" ref="E36:E46" si="0">_xlfn.TEXTJOIN("|",TRUE,G36,K36)</f>
-        <v>7226_0|2774_20010050</v>
+        <f t="shared" si="0"/>
+        <v>8677_0|1323_20010140</v>
       </c>
       <c r="F36">
         <v>99999</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" ref="G36:G46" si="1">_xlfn.TEXTJOIN("_",TRUE,H36:I36)</f>
-        <v>7226_0</v>
+        <f t="shared" si="1"/>
+        <v>8677_0</v>
       </c>
       <c r="H36">
-        <v>7226</v>
+        <v>8677</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2113,43 +2431,43 @@
         <v>34</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" ref="K36:K46" si="2">_xlfn.TEXTJOIN("_",TRUE,L36:M36)</f>
-        <v>2774_20010050</v>
+        <f t="shared" si="2"/>
+        <v>1323_20010140</v>
       </c>
       <c r="L36">
-        <f t="shared" ref="L36:L46" si="3">10000-H36</f>
-        <v>2774</v>
+        <f t="shared" si="3"/>
+        <v>1323</v>
       </c>
       <c r="M36">
-        <v>20010050</v>
+        <v>20010140</v>
       </c>
       <c r="N36" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1">
-        <v>10010060</v>
+        <v>10010150</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C37">
-        <v>10060</v>
+        <v>10150</v>
       </c>
       <c r="E37" t="str">
         <f t="shared" si="0"/>
-        <v>6588_0|3412_20010060</v>
+        <v>8981_0|1019_20010150</v>
       </c>
       <c r="F37">
         <v>99999</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="1"/>
-        <v>6588_0</v>
+        <v>8981_0</v>
       </c>
       <c r="H37">
-        <v>6588</v>
+        <v>8981</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2159,87 +2477,81 @@
       </c>
       <c r="K37" t="str">
         <f t="shared" si="2"/>
-        <v>3412_20010060</v>
+        <v>1019_20010150</v>
       </c>
       <c r="L37">
         <f t="shared" si="3"/>
-        <v>3412</v>
+        <v>1019</v>
       </c>
       <c r="M37">
-        <v>20010060</v>
+        <v>20010150</v>
       </c>
       <c r="N37" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="1">
-        <v>10010070</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38">
-        <v>10070</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:10">
+      <c r="A38">
+        <f t="shared" ref="A38:A43" si="4">C38*100+D38</f>
+        <v>101030101</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1010301</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
       </c>
       <c r="E38" t="str">
         <f t="shared" si="0"/>
-        <v>7788_0|2212_20010070</v>
+        <v>10000_20020001</v>
       </c>
       <c r="F38">
         <v>99999</v>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="1"/>
-        <v>7788_0</v>
+        <v>10000_20020001</v>
       </c>
       <c r="H38">
-        <v>7788</v>
+        <v>10000</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>20020001</v>
       </c>
       <c r="J38" t="s">
-        <v>34</v>
-      </c>
-      <c r="K38" t="str">
-        <f t="shared" si="2"/>
-        <v>2212_20010070</v>
-      </c>
-      <c r="L38">
-        <f t="shared" si="3"/>
-        <v>2212</v>
-      </c>
-      <c r="M38">
-        <v>20010070</v>
-      </c>
-      <c r="N38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="1">
-        <v>10010080</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39">
-        <v>10080</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:14">
+      <c r="A39">
+        <f t="shared" si="4"/>
+        <v>101030102</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1010301</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
       </c>
       <c r="E39" t="str">
         <f t="shared" si="0"/>
-        <v>6951_0|3049_20010080</v>
+        <v>9200_0|800_20020002</v>
       </c>
       <c r="F39">
         <v>99999</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="1"/>
-        <v>6951_0</v>
+        <v>9200_0</v>
       </c>
       <c r="H39">
-        <v>6951</v>
+        <v>9200</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2248,88 +2560,81 @@
         <v>34</v>
       </c>
       <c r="K39" t="str">
-        <f t="shared" si="2"/>
-        <v>3049_20010080</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,L39:M39)</f>
+        <v>800_20020002</v>
       </c>
       <c r="L39">
-        <f t="shared" si="3"/>
-        <v>3049</v>
+        <v>800</v>
       </c>
       <c r="M39">
-        <v>20010080</v>
+        <v>20020002</v>
       </c>
       <c r="N39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="1">
-        <v>10010090</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40">
-        <v>10090</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:10">
+      <c r="A40">
+        <f t="shared" si="4"/>
+        <v>101030201</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1010302</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
       </c>
       <c r="E40" t="str">
         <f t="shared" si="0"/>
-        <v>7861_0|2139_20010090</v>
+        <v>10000_20020011</v>
       </c>
       <c r="F40">
         <v>99999</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="1"/>
-        <v>7861_0</v>
+        <v>10000_20020011</v>
       </c>
       <c r="H40">
-        <v>7861</v>
+        <v>10000</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>20020011</v>
       </c>
       <c r="J40" t="s">
-        <v>34</v>
-      </c>
-      <c r="K40" t="str">
-        <f t="shared" si="2"/>
-        <v>2139_20010090</v>
-      </c>
-      <c r="L40">
-        <f t="shared" si="3"/>
-        <v>2139</v>
-      </c>
-      <c r="M40">
-        <v>20010090</v>
-      </c>
-      <c r="N40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="1">
-        <v>10010100</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41">
-        <v>10100</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:14">
+      <c r="A41">
+        <f t="shared" si="4"/>
+        <v>101030202</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1010302</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
       </c>
       <c r="E41" t="str">
         <f t="shared" si="0"/>
-        <v>7826_0|2174_20010100</v>
+        <v>4600_0|5400_20020002</v>
       </c>
       <c r="F41">
         <v>99999</v>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="1"/>
-        <v>7826_0</v>
+        <v>4600_0</v>
       </c>
       <c r="H41">
-        <v>7826</v>
+        <v>4600</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2338,178 +2643,151 @@
         <v>34</v>
       </c>
       <c r="K41" t="str">
-        <f t="shared" si="2"/>
-        <v>2174_20010100</v>
+        <f t="shared" ref="K41:K45" si="5">_xlfn.TEXTJOIN("_",TRUE,L41:M41)</f>
+        <v>5400_20020002</v>
       </c>
       <c r="L41">
-        <f t="shared" si="3"/>
-        <v>2174</v>
+        <v>5400</v>
       </c>
       <c r="M41">
-        <v>20010100</v>
+        <v>20020002</v>
       </c>
       <c r="N41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="1">
-        <v>10010110</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42">
-        <v>10110</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:10">
+      <c r="A42">
+        <f t="shared" si="4"/>
+        <v>101030301</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1010303</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
       </c>
       <c r="E42" t="str">
         <f t="shared" si="0"/>
-        <v>7858_0|2142_20010110</v>
+        <v>10000_20020011</v>
       </c>
       <c r="F42">
         <v>99999</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="1"/>
-        <v>7858_0</v>
+        <v>10000_20020011</v>
       </c>
       <c r="H42">
-        <v>7858</v>
+        <v>10000</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>20020011</v>
       </c>
       <c r="J42" t="s">
-        <v>34</v>
-      </c>
-      <c r="K42" t="str">
-        <f t="shared" si="2"/>
-        <v>2142_20010110</v>
-      </c>
-      <c r="L42">
-        <f t="shared" si="3"/>
-        <v>2142</v>
-      </c>
-      <c r="M42">
-        <v>20010110</v>
-      </c>
-      <c r="N42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="1">
-        <v>10010120</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43">
-        <v>10120</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:10">
+      <c r="A43">
+        <f t="shared" si="4"/>
+        <v>101030302</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1010303</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
       </c>
       <c r="E43" t="str">
         <f t="shared" si="0"/>
-        <v>7779_0|2221_20010120</v>
+        <v>10000_20020011</v>
       </c>
       <c r="F43">
         <v>99999</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="1"/>
-        <v>7779_0</v>
+        <v>10000_20020011</v>
       </c>
       <c r="H43">
-        <v>7779</v>
+        <v>10000</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>20020011</v>
       </c>
       <c r="J43" t="s">
-        <v>34</v>
-      </c>
-      <c r="K43" t="str">
-        <f t="shared" si="2"/>
-        <v>2221_20010120</v>
-      </c>
-      <c r="L43">
-        <f t="shared" si="3"/>
-        <v>2221</v>
-      </c>
-      <c r="M43">
-        <v>20010120</v>
-      </c>
-      <c r="N43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="1">
-        <v>10010130</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44">
-        <v>10130</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:10">
+      <c r="A44">
+        <f t="shared" ref="A44:A48" si="6">C44*100+D44</f>
+        <v>101030303</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="7">
+        <v>1010303</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
       </c>
       <c r="E44" t="str">
-        <f t="shared" si="0"/>
-        <v>7828_0|2172_20010130</v>
+        <f t="shared" ref="E44:E48" si="7">_xlfn.TEXTJOIN("|",TRUE,G44,K44)</f>
+        <v>10000_20020012</v>
       </c>
       <c r="F44">
         <v>99999</v>
       </c>
       <c r="G44" t="str">
-        <f t="shared" si="1"/>
-        <v>7828_0</v>
+        <f t="shared" ref="G44:G48" si="8">_xlfn.TEXTJOIN("_",TRUE,H44:I44)</f>
+        <v>10000_20020012</v>
       </c>
       <c r="H44">
-        <v>7828</v>
+        <v>10000</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>20020012</v>
       </c>
       <c r="J44" t="s">
-        <v>34</v>
-      </c>
-      <c r="K44" t="str">
-        <f t="shared" si="2"/>
-        <v>2172_20010130</v>
-      </c>
-      <c r="L44">
-        <f t="shared" si="3"/>
-        <v>2172</v>
-      </c>
-      <c r="M44">
-        <v>20010130</v>
-      </c>
-      <c r="N44" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="1">
-        <v>10010140</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45">
-        <v>10140</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:14">
+      <c r="A45">
+        <f t="shared" si="6"/>
+        <v>101030304</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1010303</v>
+      </c>
+      <c r="D45">
+        <v>4</v>
       </c>
       <c r="E45" t="str">
-        <f t="shared" si="0"/>
-        <v>8677_0|1323_20010140</v>
+        <f t="shared" si="7"/>
+        <v>2800_0|7200_20020003</v>
       </c>
       <c r="F45">
         <v>99999</v>
       </c>
       <c r="G45" t="str">
-        <f t="shared" si="1"/>
-        <v>8677_0</v>
+        <f t="shared" si="8"/>
+        <v>2800_0</v>
       </c>
       <c r="H45">
-        <v>8677</v>
+        <v>2800</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2518,63 +2796,673 @@
         <v>34</v>
       </c>
       <c r="K45" t="str">
-        <f t="shared" si="2"/>
-        <v>1323_20010140</v>
+        <f t="shared" si="5"/>
+        <v>7200_20020003</v>
       </c>
       <c r="L45">
-        <f t="shared" si="3"/>
-        <v>1323</v>
+        <v>7200</v>
       </c>
       <c r="M45">
-        <v>20010140</v>
+        <v>20020003</v>
       </c>
       <c r="N45" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:10">
+      <c r="A46">
+        <f t="shared" si="6"/>
+        <v>101030401</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="9">
+        <v>1010304</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="7"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="F46">
+        <v>99999</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="8"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="H46">
+        <v>10000</v>
+      </c>
+      <c r="I46">
+        <v>20020011</v>
+      </c>
+      <c r="J46" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="1">
-        <v>10010150</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46">
-        <v>10150</v>
-      </c>
-      <c r="E46" t="str">
-        <f t="shared" si="0"/>
-        <v>8981_0|1019_20010150</v>
-      </c>
-      <c r="F46">
-        <v>99999</v>
-      </c>
-      <c r="G46" t="str">
-        <f t="shared" si="1"/>
-        <v>8981_0</v>
-      </c>
-      <c r="H46">
-        <v>8981</v>
-      </c>
-      <c r="I46">
+    <row r="47" customFormat="1" spans="1:10">
+      <c r="A47">
+        <f t="shared" si="6"/>
+        <v>101030402</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="9">
+        <v>1010304</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="7"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="F47">
+        <v>99999</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="8"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="H47">
+        <v>10000</v>
+      </c>
+      <c r="I47">
+        <v>20020011</v>
+      </c>
+      <c r="J47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:10">
+      <c r="A48">
+        <f t="shared" si="6"/>
+        <v>101030403</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="9">
+        <v>1010304</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="7"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="F48">
+        <v>99999</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="8"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="H48">
+        <v>10000</v>
+      </c>
+      <c r="I48">
+        <v>20020011</v>
+      </c>
+      <c r="J48" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:10">
+      <c r="A49">
+        <f t="shared" ref="A49:A51" si="9">C49*100+D49</f>
+        <v>101030404</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="9">
+        <v>1010304</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49" t="str">
+        <f t="shared" ref="E49:E51" si="10">_xlfn.TEXTJOIN("|",TRUE,G49,K49)</f>
+        <v>10000_20020012</v>
+      </c>
+      <c r="F49">
+        <v>99999</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" ref="G49:G51" si="11">_xlfn.TEXTJOIN("_",TRUE,H49:I49)</f>
+        <v>10000_20020012</v>
+      </c>
+      <c r="H49">
+        <v>10000</v>
+      </c>
+      <c r="I49">
+        <v>20020012</v>
+      </c>
+      <c r="J49" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:10">
+      <c r="A50">
+        <f t="shared" si="9"/>
+        <v>101030405</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="9">
+        <v>1010304</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="10"/>
+        <v>10000_20020002</v>
+      </c>
+      <c r="F50">
+        <v>99999</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="11"/>
+        <v>10000_20020002</v>
+      </c>
+      <c r="H50">
+        <v>10000</v>
+      </c>
+      <c r="I50">
+        <v>20020002</v>
+      </c>
+      <c r="J50" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:10">
+      <c r="A51">
+        <f t="shared" si="9"/>
+        <v>101030406</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" s="9">
+        <v>1010304</v>
+      </c>
+      <c r="D51">
+        <v>6</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" si="10"/>
+        <v>10000_20020003</v>
+      </c>
+      <c r="F51">
+        <v>99999</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="11"/>
+        <v>10000_20020003</v>
+      </c>
+      <c r="H51">
+        <v>10000</v>
+      </c>
+      <c r="I51">
+        <v>20020003</v>
+      </c>
+      <c r="J51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:14">
+      <c r="A52">
+        <f t="shared" ref="A52:A57" si="12">C52*100+D52</f>
+        <v>101030407</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" s="9">
+        <v>1010304</v>
+      </c>
+      <c r="D52">
+        <v>7</v>
+      </c>
+      <c r="E52" t="str">
+        <f t="shared" ref="E52:E57" si="13">_xlfn.TEXTJOIN("|",TRUE,G52,K52)</f>
+        <v>4800_0|5200_20020004</v>
+      </c>
+      <c r="F52">
+        <v>99999</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" ref="G52:G57" si="14">_xlfn.TEXTJOIN("_",TRUE,H52:I52)</f>
+        <v>4800_0</v>
+      </c>
+      <c r="H52">
+        <v>4800</v>
+      </c>
+      <c r="I52">
         <v>0</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J52" t="s">
         <v>34</v>
       </c>
-      <c r="K46" t="str">
-        <f t="shared" si="2"/>
-        <v>1019_20010150</v>
-      </c>
-      <c r="L46">
-        <f t="shared" si="3"/>
-        <v>1019</v>
-      </c>
-      <c r="M46">
-        <v>20010150</v>
-      </c>
-      <c r="N46" t="s">
-        <v>64</v>
+      <c r="K52" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L52:M52)</f>
+        <v>5200_20020004</v>
+      </c>
+      <c r="L52">
+        <v>5200</v>
+      </c>
+      <c r="M52">
+        <v>20020004</v>
+      </c>
+      <c r="N52" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:10">
+      <c r="A53">
+        <f t="shared" si="12"/>
+        <v>101030501</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="str">
+        <f t="shared" si="13"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="F53">
+        <v>99999</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="14"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="H53">
+        <v>10000</v>
+      </c>
+      <c r="I53">
+        <v>20020011</v>
+      </c>
+      <c r="J53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:10">
+      <c r="A54">
+        <f t="shared" si="12"/>
+        <v>101030502</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="13"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="F54">
+        <v>99999</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="14"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="H54">
+        <v>10000</v>
+      </c>
+      <c r="I54">
+        <v>20020011</v>
+      </c>
+      <c r="J54" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:10">
+      <c r="A55">
+        <f t="shared" si="12"/>
+        <v>101030503</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="13"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="F55">
+        <v>99999</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="14"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="H55">
+        <v>10000</v>
+      </c>
+      <c r="I55">
+        <v>20020011</v>
+      </c>
+      <c r="J55" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:10">
+      <c r="A56">
+        <f t="shared" si="12"/>
+        <v>101030504</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56" t="str">
+        <f t="shared" si="13"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="F56">
+        <v>99999</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="14"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="H56">
+        <v>10000</v>
+      </c>
+      <c r="I56">
+        <v>20020011</v>
+      </c>
+      <c r="J56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:10">
+      <c r="A57">
+        <f t="shared" si="12"/>
+        <v>101030505</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+      <c r="E57" t="str">
+        <f t="shared" si="13"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="F57">
+        <v>99999</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="14"/>
+        <v>10000_20020011</v>
+      </c>
+      <c r="H57">
+        <v>10000</v>
+      </c>
+      <c r="I57">
+        <v>20020011</v>
+      </c>
+      <c r="J57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:10">
+      <c r="A58">
+        <f t="shared" ref="A58:A60" si="15">C58*100+D58</f>
+        <v>101030506</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D58">
+        <v>6</v>
+      </c>
+      <c r="E58" t="str">
+        <f t="shared" ref="E58:E60" si="16">_xlfn.TEXTJOIN("|",TRUE,G58,K58)</f>
+        <v>10000_20020012</v>
+      </c>
+      <c r="F58">
+        <v>99999</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" ref="G58:G60" si="17">_xlfn.TEXTJOIN("_",TRUE,H58:I58)</f>
+        <v>10000_20020012</v>
+      </c>
+      <c r="H58">
+        <v>10000</v>
+      </c>
+      <c r="I58">
+        <v>20020012</v>
+      </c>
+      <c r="J58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:10">
+      <c r="A59">
+        <f t="shared" si="15"/>
+        <v>101030507</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D59">
+        <v>7</v>
+      </c>
+      <c r="E59" t="str">
+        <f t="shared" si="16"/>
+        <v>10000_20020012</v>
+      </c>
+      <c r="F59">
+        <v>99999</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="17"/>
+        <v>10000_20020012</v>
+      </c>
+      <c r="H59">
+        <v>10000</v>
+      </c>
+      <c r="I59">
+        <v>20020012</v>
+      </c>
+      <c r="J59" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:10">
+      <c r="A60">
+        <f t="shared" si="15"/>
+        <v>101030508</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D60">
+        <v>8</v>
+      </c>
+      <c r="E60" t="str">
+        <f t="shared" si="16"/>
+        <v>10000_20020012</v>
+      </c>
+      <c r="F60">
+        <v>99999</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="17"/>
+        <v>10000_20020012</v>
+      </c>
+      <c r="H60">
+        <v>10000</v>
+      </c>
+      <c r="I60">
+        <v>20020012</v>
+      </c>
+      <c r="J60" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:10">
+      <c r="A61">
+        <f>C61*100+D61</f>
+        <v>101030509</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D61">
+        <v>9</v>
+      </c>
+      <c r="E61" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G61,K61)</f>
+        <v>10000_20020013</v>
+      </c>
+      <c r="F61">
+        <v>99999</v>
+      </c>
+      <c r="G61" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H61:I61)</f>
+        <v>10000_20020013</v>
+      </c>
+      <c r="H61">
+        <v>10000</v>
+      </c>
+      <c r="I61">
+        <v>20020013</v>
+      </c>
+      <c r="J61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:10">
+      <c r="A62">
+        <f>C62*100+D62</f>
+        <v>101030510</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D62">
+        <v>10</v>
+      </c>
+      <c r="E62" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G62,K62)</f>
+        <v>10000_20020004</v>
+      </c>
+      <c r="F62">
+        <v>99999</v>
+      </c>
+      <c r="G62" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H62:I62)</f>
+        <v>10000_20020004</v>
+      </c>
+      <c r="H62">
+        <v>10000</v>
+      </c>
+      <c r="I62">
+        <v>20020004</v>
+      </c>
+      <c r="J62" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:14">
+      <c r="A63">
+        <f>C63*100+D63</f>
+        <v>101030511</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="4">
+        <v>1010305</v>
+      </c>
+      <c r="D63">
+        <v>11</v>
+      </c>
+      <c r="E63" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G63,K63)</f>
+        <v>6500_0|3500_20020005</v>
+      </c>
+      <c r="F63">
+        <v>99999</v>
+      </c>
+      <c r="G63" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H63:I63)</f>
+        <v>6500_0</v>
+      </c>
+      <c r="H63">
+        <v>6500</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63" t="s">
+        <v>34</v>
+      </c>
+      <c r="K63" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L63:M63)</f>
+        <v>3500_20020005</v>
+      </c>
+      <c r="L63">
+        <v>3500</v>
+      </c>
+      <c r="M63">
+        <v>20020005</v>
+      </c>
+      <c r="N63" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/dropGroup.xlsx
+++ b/poker/resources/sample/dropGroup.xlsx
@@ -482,7 +482,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -497,37 +497,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -856,7 +832,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -880,16 +856,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -898,13 +874,25 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -965,23 +953,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -991,25 +967,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2498,7 +2471,7 @@
       <c r="B38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="1">
         <v>1010301</v>
       </c>
       <c r="D38">
@@ -2533,7 +2506,7 @@
       <c r="B39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="1">
         <v>1010301</v>
       </c>
       <c r="D39">
@@ -2578,10 +2551,10 @@
         <f t="shared" si="4"/>
         <v>101030201</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="4">
         <v>1010302</v>
       </c>
       <c r="D40">
@@ -2613,10 +2586,10 @@
         <f t="shared" si="4"/>
         <v>101030202</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="4">
         <v>1010302</v>
       </c>
       <c r="D41">
@@ -2661,10 +2634,10 @@
         <f t="shared" si="4"/>
         <v>101030301</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="6">
         <v>1010303</v>
       </c>
       <c r="D42">
@@ -2696,10 +2669,10 @@
         <f t="shared" si="4"/>
         <v>101030302</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="6">
         <v>1010303</v>
       </c>
       <c r="D43">
@@ -2731,10 +2704,10 @@
         <f t="shared" ref="A44:A48" si="6">C44*100+D44</f>
         <v>101030303</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="6">
         <v>1010303</v>
       </c>
       <c r="D44">
@@ -2766,10 +2739,10 @@
         <f t="shared" si="6"/>
         <v>101030304</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="6">
         <v>1010303</v>
       </c>
       <c r="D45">
@@ -2814,10 +2787,10 @@
         <f t="shared" si="6"/>
         <v>101030401</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="8">
         <v>1010304</v>
       </c>
       <c r="D46">
@@ -2849,10 +2822,10 @@
         <f t="shared" si="6"/>
         <v>101030402</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="8">
         <v>1010304</v>
       </c>
       <c r="D47">
@@ -2884,10 +2857,10 @@
         <f t="shared" si="6"/>
         <v>101030403</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="8">
         <v>1010304</v>
       </c>
       <c r="D48">
@@ -2919,10 +2892,10 @@
         <f t="shared" ref="A49:A51" si="9">C49*100+D49</f>
         <v>101030404</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="8">
         <v>1010304</v>
       </c>
       <c r="D49">
@@ -2954,10 +2927,10 @@
         <f t="shared" si="9"/>
         <v>101030405</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="8">
         <v>1010304</v>
       </c>
       <c r="D50">
@@ -2989,10 +2962,10 @@
         <f t="shared" si="9"/>
         <v>101030406</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="8">
         <v>1010304</v>
       </c>
       <c r="D51">
@@ -3024,10 +2997,10 @@
         <f t="shared" ref="A52:A57" si="12">C52*100+D52</f>
         <v>101030407</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <v>1010304</v>
       </c>
       <c r="D52">
@@ -3072,10 +3045,10 @@
         <f t="shared" si="12"/>
         <v>101030501</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="3">
         <v>1010305</v>
       </c>
       <c r="D53">
@@ -3107,10 +3080,10 @@
         <f t="shared" si="12"/>
         <v>101030502</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="3">
         <v>1010305</v>
       </c>
       <c r="D54">
@@ -3142,10 +3115,10 @@
         <f t="shared" si="12"/>
         <v>101030503</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="3">
         <v>1010305</v>
       </c>
       <c r="D55">
@@ -3177,10 +3150,10 @@
         <f t="shared" si="12"/>
         <v>101030504</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="3">
         <v>1010305</v>
       </c>
       <c r="D56">
@@ -3212,10 +3185,10 @@
         <f t="shared" si="12"/>
         <v>101030505</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="3">
         <v>1010305</v>
       </c>
       <c r="D57">
@@ -3244,27 +3217,27 @@
     </row>
     <row r="58" customFormat="1" spans="1:10">
       <c r="A58">
-        <f t="shared" ref="A58:A60" si="15">C58*100+D58</f>
+        <f t="shared" ref="A58:A63" si="15">C58*100+D58</f>
         <v>101030506</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="3">
         <v>1010305</v>
       </c>
       <c r="D58">
         <v>6</v>
       </c>
       <c r="E58" t="str">
-        <f t="shared" ref="E58:E60" si="16">_xlfn.TEXTJOIN("|",TRUE,G58,K58)</f>
+        <f t="shared" ref="E58:E63" si="16">_xlfn.TEXTJOIN("|",TRUE,G58,K58)</f>
         <v>10000_20020012</v>
       </c>
       <c r="F58">
         <v>99999</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" ref="G58:G60" si="17">_xlfn.TEXTJOIN("_",TRUE,H58:I58)</f>
+        <f t="shared" ref="G58:G63" si="17">_xlfn.TEXTJOIN("_",TRUE,H58:I58)</f>
         <v>10000_20020012</v>
       </c>
       <c r="H58">
@@ -3282,10 +3255,10 @@
         <f t="shared" si="15"/>
         <v>101030507</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="3">
         <v>1010305</v>
       </c>
       <c r="D59">
@@ -3317,10 +3290,10 @@
         <f t="shared" si="15"/>
         <v>101030508</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="3">
         <v>1010305</v>
       </c>
       <c r="D60">
@@ -3349,27 +3322,27 @@
     </row>
     <row r="61" customFormat="1" spans="1:10">
       <c r="A61">
-        <f>C61*100+D61</f>
+        <f t="shared" si="15"/>
         <v>101030509</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="3">
         <v>1010305</v>
       </c>
       <c r="D61">
         <v>9</v>
       </c>
       <c r="E61" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G61,K61)</f>
+        <f t="shared" si="16"/>
         <v>10000_20020013</v>
       </c>
       <c r="F61">
         <v>99999</v>
       </c>
       <c r="G61" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H61:I61)</f>
+        <f t="shared" si="17"/>
         <v>10000_20020013</v>
       </c>
       <c r="H61">
@@ -3384,27 +3357,27 @@
     </row>
     <row r="62" customFormat="1" spans="1:10">
       <c r="A62">
-        <f>C62*100+D62</f>
+        <f t="shared" si="15"/>
         <v>101030510</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="3">
         <v>1010305</v>
       </c>
       <c r="D62">
         <v>10</v>
       </c>
       <c r="E62" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G62,K62)</f>
+        <f t="shared" si="16"/>
         <v>10000_20020004</v>
       </c>
       <c r="F62">
         <v>99999</v>
       </c>
       <c r="G62" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H62:I62)</f>
+        <f t="shared" si="17"/>
         <v>10000_20020004</v>
       </c>
       <c r="H62">
@@ -3419,27 +3392,27 @@
     </row>
     <row r="63" customFormat="1" spans="1:14">
       <c r="A63">
-        <f>C63*100+D63</f>
+        <f t="shared" si="15"/>
         <v>101030511</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="3">
         <v>1010305</v>
       </c>
       <c r="D63">
         <v>11</v>
       </c>
       <c r="E63" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G63,K63)</f>
+        <f t="shared" si="16"/>
         <v>6500_0|3500_20020005</v>
       </c>
       <c r="F63">
         <v>99999</v>
       </c>
       <c r="G63" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H63:I63)</f>
+        <f t="shared" si="17"/>
         <v>6500_0</v>
       </c>
       <c r="H63">

--- a/poker/resources/sample/dropGroup.xlsx
+++ b/poker/resources/sample/dropGroup.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -266,40 +266,22 @@
     <t>赌场工具（普通）</t>
   </si>
   <si>
-    <t>1星材料包</t>
-  </si>
-  <si>
-    <t>2星材料包</t>
+    <t>1星材料包-35</t>
+  </si>
+  <si>
+    <t>1星材料包-40</t>
   </si>
   <si>
     <t>赌场工具（精良）</t>
   </si>
   <si>
-    <t>1星材料包X2</t>
-  </si>
-  <si>
     <t>赌场工具（优秀）</t>
   </si>
   <si>
-    <t>2星材料包X2</t>
-  </si>
-  <si>
-    <t>3星材料包</t>
-  </si>
-  <si>
     <t>赌场工具（绝佳）</t>
   </si>
   <si>
-    <t>4星材料包</t>
-  </si>
-  <si>
     <t>赌场工具（传奇）</t>
-  </si>
-  <si>
-    <t>3星材料包X2</t>
-  </si>
-  <si>
-    <t>5星材料包</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1279,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -1355,7 +1337,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1369,7 +1351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1603,7 +1585,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>10000601</v>
       </c>
@@ -1623,7 +1605,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>10000602</v>
       </c>
@@ -1643,7 +1625,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>10000603</v>
       </c>
@@ -1663,7 +1645,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>10000611</v>
       </c>
@@ -1683,7 +1665,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>10000612</v>
       </c>
@@ -1703,7 +1685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>10000613</v>
       </c>
@@ -1723,7 +1705,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>10000621</v>
       </c>
@@ -1743,7 +1725,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>10000622</v>
       </c>
@@ -1763,7 +1745,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>10000623</v>
       </c>
@@ -1783,7 +1765,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:6">
+    <row r="19" customFormat="1" spans="1:14">
       <c r="A19">
         <v>10000631</v>
       </c>
@@ -1803,7 +1785,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:6">
+    <row r="20" customFormat="1" spans="1:14">
       <c r="A20">
         <v>10000632</v>
       </c>
@@ -1823,7 +1805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:6">
+    <row r="21" customFormat="1" spans="1:14">
       <c r="A21">
         <v>10000633</v>
       </c>
@@ -1843,7 +1825,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:6">
+    <row r="22" customFormat="1" spans="1:14">
       <c r="A22">
         <v>10000641</v>
       </c>
@@ -1863,7 +1845,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:6">
+    <row r="23" customFormat="1" spans="1:14">
       <c r="A23">
         <v>10000642</v>
       </c>
@@ -1883,7 +1865,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" customFormat="1" spans="1:6">
+    <row r="24" customFormat="1" spans="1:14">
       <c r="A24">
         <v>10000643</v>
       </c>
@@ -1903,7 +1885,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>10000651</v>
       </c>
@@ -1986,7 +1968,7 @@
         <v>99999</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" ref="G27:G43" si="1">_xlfn.TEXTJOIN("_",TRUE,H27:I27)</f>
+        <f t="shared" ref="G27:G49" si="1">_xlfn.TEXTJOIN("_",TRUE,H27:I27)</f>
         <v>7226_0</v>
       </c>
       <c r="H27">
@@ -2463,7 +2445,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:10">
+    <row r="38" customFormat="1" spans="1:14">
       <c r="A38">
         <f t="shared" ref="A38:A43" si="4">C38*100+D38</f>
         <v>101030101</v>
@@ -2479,20 +2461,20 @@
       </c>
       <c r="E38" t="str">
         <f t="shared" si="0"/>
-        <v>10000_20020001</v>
+        <v>10000_20020020</v>
       </c>
       <c r="F38">
         <v>99999</v>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="1"/>
-        <v>10000_20020001</v>
+        <v>10000_20020020</v>
       </c>
       <c r="H38">
         <v>10000</v>
       </c>
       <c r="I38">
-        <v>20020001</v>
+        <v>20020020</v>
       </c>
       <c r="J38" t="s">
         <v>60</v>
@@ -2514,39 +2496,26 @@
       </c>
       <c r="E39" t="str">
         <f t="shared" si="0"/>
-        <v>9200_0|800_20020002</v>
+        <v>10000_20020021</v>
       </c>
       <c r="F39">
         <v>99999</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="1"/>
-        <v>9200_0</v>
+        <v>10000_20020021</v>
       </c>
       <c r="H39">
-        <v>9200</v>
+        <v>10000</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>20020021</v>
       </c>
       <c r="J39" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L39:M39)</f>
-        <v>800_20020002</v>
-      </c>
-      <c r="L39">
-        <v>800</v>
-      </c>
-      <c r="M39">
-        <v>20020002</v>
-      </c>
-      <c r="N39" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="1:10">
+    <row r="40" customFormat="1" spans="1:14">
       <c r="A40">
         <f t="shared" si="4"/>
         <v>101030201</v>
@@ -2562,23 +2531,23 @@
       </c>
       <c r="E40" t="str">
         <f t="shared" si="0"/>
-        <v>10000_20020011</v>
+        <v>10000_20020020</v>
       </c>
       <c r="F40">
         <v>99999</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="1"/>
-        <v>10000_20020011</v>
+        <v>10000_20020020</v>
       </c>
       <c r="H40">
         <v>10000</v>
       </c>
       <c r="I40">
-        <v>20020011</v>
+        <v>20020020</v>
       </c>
       <c r="J40" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:14">
@@ -2597,845 +2566,933 @@
       </c>
       <c r="E41" t="str">
         <f t="shared" si="0"/>
-        <v>4600_0|5400_20020002</v>
+        <v>10000_20020021</v>
       </c>
       <c r="F41">
         <v>99999</v>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="1"/>
-        <v>4600_0</v>
+        <v>10000_20020021</v>
       </c>
       <c r="H41">
-        <v>4600</v>
+        <v>10000</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>20020021</v>
       </c>
       <c r="J41" t="s">
-        <v>34</v>
-      </c>
-      <c r="K41" t="str">
-        <f t="shared" ref="K41:K45" si="5">_xlfn.TEXTJOIN("_",TRUE,L41:M41)</f>
-        <v>5400_20020002</v>
-      </c>
-      <c r="L41">
-        <v>5400</v>
-      </c>
-      <c r="M41">
-        <v>20020002</v>
-      </c>
-      <c r="N41" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="42" customFormat="1" spans="1:10">
+    <row r="42" customFormat="1" spans="1:14">
       <c r="A42">
         <f t="shared" si="4"/>
-        <v>101030301</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1010303</v>
+        <v>101030203</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="4">
+        <v>1010302</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" t="str">
         <f t="shared" si="0"/>
-        <v>10000_20020011</v>
+        <v>10000_20020020</v>
       </c>
       <c r="F42">
         <v>99999</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="1"/>
-        <v>10000_20020011</v>
+        <v>10000_20020020</v>
       </c>
       <c r="H42">
         <v>10000</v>
       </c>
       <c r="I42">
-        <v>20020011</v>
+        <v>20020020</v>
       </c>
       <c r="J42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:14">
       <c r="A43">
         <f t="shared" si="4"/>
-        <v>101030302</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1010303</v>
+        <v>101030204</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="4">
+        <v>1010302</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" t="str">
         <f t="shared" si="0"/>
-        <v>10000_20020011</v>
+        <v>10000_20020021</v>
       </c>
       <c r="F43">
         <v>99999</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="1"/>
-        <v>10000_20020011</v>
+        <v>10000_20020021</v>
       </c>
       <c r="H43">
         <v>10000</v>
       </c>
       <c r="I43">
-        <v>20020011</v>
+        <v>20020021</v>
       </c>
       <c r="J43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:14">
+      <c r="A44">
+        <f t="shared" ref="A44:A49" si="5">C44*100+D44</f>
+        <v>101030301</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" spans="1:10">
-      <c r="A44">
-        <f t="shared" ref="A44:A48" si="6">C44*100+D44</f>
-        <v>101030303</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="C44" s="6">
         <v>1010303</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" t="str">
-        <f t="shared" ref="E44:E48" si="7">_xlfn.TEXTJOIN("|",TRUE,G44,K44)</f>
-        <v>10000_20020012</v>
+        <f t="shared" ref="E44:E49" si="6">_xlfn.TEXTJOIN("|",TRUE,G44,K44)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="F44">
         <v>99999</v>
       </c>
       <c r="G44" t="str">
-        <f t="shared" ref="G44:G48" si="8">_xlfn.TEXTJOIN("_",TRUE,H44:I44)</f>
-        <v>10000_20020012</v>
+        <f t="shared" si="1"/>
+        <v>10000_20020020</v>
       </c>
       <c r="H44">
         <v>10000</v>
       </c>
       <c r="I44">
-        <v>20020012</v>
+        <v>20020020</v>
       </c>
       <c r="J44" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:14">
       <c r="A45">
-        <f t="shared" si="6"/>
-        <v>101030304</v>
+        <f t="shared" si="5"/>
+        <v>101030302</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C45" s="6">
         <v>1010303</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="str">
-        <f t="shared" si="7"/>
-        <v>2800_0|7200_20020003</v>
+        <f t="shared" si="6"/>
+        <v>10000_20020021</v>
       </c>
       <c r="F45">
         <v>99999</v>
       </c>
       <c r="G45" t="str">
-        <f t="shared" si="8"/>
-        <v>2800_0</v>
+        <f t="shared" si="1"/>
+        <v>10000_20020021</v>
       </c>
       <c r="H45">
-        <v>2800</v>
+        <v>10000</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>20020021</v>
       </c>
       <c r="J45" t="s">
-        <v>34</v>
-      </c>
-      <c r="K45" t="str">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:14">
+      <c r="A46">
         <f t="shared" si="5"/>
-        <v>7200_20020003</v>
-      </c>
-      <c r="L45">
-        <v>7200</v>
-      </c>
-      <c r="M45">
-        <v>20020003</v>
-      </c>
-      <c r="N45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:10">
-      <c r="A46">
+        <v>101030303</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="6">
+        <v>1010303</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46" t="str">
         <f t="shared" si="6"/>
-        <v>101030401</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="8">
-        <v>1010304</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" t="str">
-        <f t="shared" si="7"/>
-        <v>10000_20020011</v>
+        <v>10000_20020020</v>
       </c>
       <c r="F46">
         <v>99999</v>
       </c>
       <c r="G46" t="str">
-        <f t="shared" si="8"/>
-        <v>10000_20020011</v>
+        <f t="shared" si="1"/>
+        <v>10000_20020020</v>
       </c>
       <c r="H46">
         <v>10000</v>
       </c>
       <c r="I46">
-        <v>20020011</v>
+        <v>20020020</v>
       </c>
       <c r="J46" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:14">
+      <c r="A47">
+        <f t="shared" si="5"/>
+        <v>101030304</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:10">
-      <c r="A47">
+      <c r="C47" s="6">
+        <v>1010303</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" t="str">
         <f t="shared" si="6"/>
-        <v>101030402</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="8">
-        <v>1010304</v>
-      </c>
-      <c r="D47">
-        <v>2</v>
-      </c>
-      <c r="E47" t="str">
-        <f t="shared" si="7"/>
-        <v>10000_20020011</v>
+        <v>10000_20020021</v>
       </c>
       <c r="F47">
         <v>99999</v>
       </c>
       <c r="G47" t="str">
-        <f t="shared" si="8"/>
-        <v>10000_20020011</v>
+        <f t="shared" si="1"/>
+        <v>10000_20020021</v>
       </c>
       <c r="H47">
         <v>10000</v>
       </c>
       <c r="I47">
-        <v>20020011</v>
+        <v>20020021</v>
       </c>
       <c r="J47" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:14">
+      <c r="A48">
+        <f t="shared" si="5"/>
+        <v>101030305</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:10">
-      <c r="A48">
+      <c r="C48" s="6">
+        <v>1010303</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48" t="str">
         <f t="shared" si="6"/>
-        <v>101030403</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="8">
-        <v>1010304</v>
-      </c>
-      <c r="D48">
-        <v>3</v>
-      </c>
-      <c r="E48" t="str">
-        <f t="shared" si="7"/>
-        <v>10000_20020011</v>
+        <v>10000_20020020</v>
       </c>
       <c r="F48">
         <v>99999</v>
       </c>
       <c r="G48" t="str">
-        <f t="shared" si="8"/>
-        <v>10000_20020011</v>
+        <f t="shared" si="1"/>
+        <v>10000_20020020</v>
       </c>
       <c r="H48">
         <v>10000</v>
       </c>
       <c r="I48">
-        <v>20020011</v>
+        <v>20020020</v>
       </c>
       <c r="J48" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:10">
       <c r="A49">
-        <f t="shared" ref="A49:A51" si="9">C49*100+D49</f>
-        <v>101030404</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="8">
-        <v>1010304</v>
+        <f t="shared" si="5"/>
+        <v>101030306</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="6">
+        <v>1010303</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E49" t="str">
-        <f t="shared" ref="E49:E51" si="10">_xlfn.TEXTJOIN("|",TRUE,G49,K49)</f>
-        <v>10000_20020012</v>
+        <f t="shared" si="6"/>
+        <v>10000_20020021</v>
       </c>
       <c r="F49">
         <v>99999</v>
       </c>
       <c r="G49" t="str">
-        <f t="shared" ref="G49:G51" si="11">_xlfn.TEXTJOIN("_",TRUE,H49:I49)</f>
-        <v>10000_20020012</v>
+        <f t="shared" si="1"/>
+        <v>10000_20020021</v>
       </c>
       <c r="H49">
         <v>10000</v>
       </c>
       <c r="I49">
-        <v>20020012</v>
+        <v>20020021</v>
       </c>
       <c r="J49" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:10">
       <c r="A50">
-        <f t="shared" si="9"/>
-        <v>101030405</v>
+        <f>C50*100+D50</f>
+        <v>101030401</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C50" s="8">
         <v>1010304</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E50" t="str">
-        <f t="shared" si="10"/>
-        <v>10000_20020002</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G50,K50)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="F50">
         <v>99999</v>
       </c>
       <c r="G50" t="str">
-        <f t="shared" si="11"/>
-        <v>10000_20020002</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H50:I50)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="H50">
         <v>10000</v>
       </c>
       <c r="I50">
-        <v>20020002</v>
+        <v>20020020</v>
       </c>
       <c r="J50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:10">
       <c r="A51">
-        <f t="shared" si="9"/>
-        <v>101030406</v>
+        <f>C51*100+D51</f>
+        <v>101030402</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C51" s="8">
         <v>1010304</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E51" t="str">
-        <f t="shared" si="10"/>
-        <v>10000_20020003</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G51,K51)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="F51">
         <v>99999</v>
       </c>
       <c r="G51" t="str">
-        <f t="shared" si="11"/>
-        <v>10000_20020003</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H51:I51)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="H51">
         <v>10000</v>
       </c>
       <c r="I51">
-        <v>20020003</v>
+        <v>20020021</v>
       </c>
       <c r="J51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" spans="1:14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:10">
       <c r="A52">
-        <f t="shared" ref="A52:A57" si="12">C52*100+D52</f>
-        <v>101030407</v>
+        <f t="shared" ref="A52:A57" si="7">C52*100+D52</f>
+        <v>101030403</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C52" s="8">
         <v>1010304</v>
       </c>
       <c r="D52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E52" t="str">
-        <f t="shared" ref="E52:E57" si="13">_xlfn.TEXTJOIN("|",TRUE,G52,K52)</f>
-        <v>4800_0|5200_20020004</v>
+        <f t="shared" ref="E52:E57" si="8">_xlfn.TEXTJOIN("|",TRUE,G52,K52)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="F52">
         <v>99999</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" ref="G52:G57" si="14">_xlfn.TEXTJOIN("_",TRUE,H52:I52)</f>
-        <v>4800_0</v>
+        <f t="shared" ref="G52:G57" si="9">_xlfn.TEXTJOIN("_",TRUE,H52:I52)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="H52">
-        <v>4800</v>
+        <v>10000</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>20020020</v>
       </c>
       <c r="J52" t="s">
-        <v>34</v>
-      </c>
-      <c r="K52" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L52:M52)</f>
-        <v>5200_20020004</v>
-      </c>
-      <c r="L52">
-        <v>5200</v>
-      </c>
-      <c r="M52">
-        <v>20020004</v>
-      </c>
-      <c r="N52" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:10">
       <c r="A53">
-        <f t="shared" si="12"/>
-        <v>101030501</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C53" s="3">
-        <v>1010305</v>
+        <f t="shared" ref="A53:A55" si="10">C53*100+D53</f>
+        <v>101030404</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1010304</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53" t="str">
-        <f t="shared" si="13"/>
-        <v>10000_20020011</v>
+        <f t="shared" ref="E53:E55" si="11">_xlfn.TEXTJOIN("|",TRUE,G53,K53)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="F53">
         <v>99999</v>
       </c>
       <c r="G53" t="str">
-        <f t="shared" si="14"/>
-        <v>10000_20020011</v>
+        <f t="shared" ref="G53:G55" si="12">_xlfn.TEXTJOIN("_",TRUE,H53:I53)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="H53">
         <v>10000</v>
       </c>
       <c r="I53">
-        <v>20020011</v>
+        <v>20020021</v>
       </c>
       <c r="J53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:10">
       <c r="A54">
+        <f t="shared" si="10"/>
+        <v>101030405</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1010304</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="11"/>
+        <v>10000_20020020</v>
+      </c>
+      <c r="F54">
+        <v>99999</v>
+      </c>
+      <c r="G54" t="str">
         <f t="shared" si="12"/>
-        <v>101030502</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C54" s="3">
-        <v>1010305</v>
-      </c>
-      <c r="D54">
-        <v>2</v>
-      </c>
-      <c r="E54" t="str">
-        <f t="shared" si="13"/>
-        <v>10000_20020011</v>
-      </c>
-      <c r="F54">
-        <v>99999</v>
-      </c>
-      <c r="G54" t="str">
-        <f t="shared" si="14"/>
-        <v>10000_20020011</v>
+        <v>10000_20020020</v>
       </c>
       <c r="H54">
         <v>10000</v>
       </c>
       <c r="I54">
-        <v>20020011</v>
+        <v>20020020</v>
       </c>
       <c r="J54" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:10">
       <c r="A55">
+        <f t="shared" si="10"/>
+        <v>101030406</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="8">
+        <v>1010304</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="11"/>
+        <v>10000_20020021</v>
+      </c>
+      <c r="F55">
+        <v>99999</v>
+      </c>
+      <c r="G55" t="str">
         <f t="shared" si="12"/>
-        <v>101030503</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" s="3">
-        <v>1010305</v>
-      </c>
-      <c r="D55">
-        <v>3</v>
-      </c>
-      <c r="E55" t="str">
-        <f t="shared" si="13"/>
-        <v>10000_20020011</v>
-      </c>
-      <c r="F55">
-        <v>99999</v>
-      </c>
-      <c r="G55" t="str">
-        <f t="shared" si="14"/>
-        <v>10000_20020011</v>
+        <v>10000_20020021</v>
       </c>
       <c r="H55">
         <v>10000</v>
       </c>
       <c r="I55">
-        <v>20020011</v>
+        <v>20020021</v>
       </c>
       <c r="J55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:10">
       <c r="A56">
-        <f t="shared" si="12"/>
-        <v>101030504</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="3">
-        <v>1010305</v>
+        <f t="shared" si="7"/>
+        <v>101030407</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="8">
+        <v>1010304</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E56" t="str">
-        <f t="shared" si="13"/>
-        <v>10000_20020011</v>
+        <f t="shared" si="8"/>
+        <v>10000_20020020</v>
       </c>
       <c r="F56">
         <v>99999</v>
       </c>
       <c r="G56" t="str">
-        <f t="shared" si="14"/>
-        <v>10000_20020011</v>
+        <f t="shared" si="9"/>
+        <v>10000_20020020</v>
       </c>
       <c r="H56">
         <v>10000</v>
       </c>
       <c r="I56">
-        <v>20020011</v>
+        <v>20020020</v>
       </c>
       <c r="J56" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:10">
       <c r="A57">
-        <f t="shared" si="12"/>
-        <v>101030505</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="3">
-        <v>1010305</v>
+        <f t="shared" si="7"/>
+        <v>101030408</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="8">
+        <v>1010304</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E57" t="str">
-        <f t="shared" si="13"/>
-        <v>10000_20020011</v>
+        <f t="shared" si="8"/>
+        <v>10000_20020021</v>
       </c>
       <c r="F57">
         <v>99999</v>
       </c>
       <c r="G57" t="str">
-        <f t="shared" si="14"/>
-        <v>10000_20020011</v>
+        <f t="shared" si="9"/>
+        <v>10000_20020021</v>
       </c>
       <c r="H57">
         <v>10000</v>
       </c>
       <c r="I57">
-        <v>20020011</v>
+        <v>20020021</v>
       </c>
       <c r="J57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:10">
       <c r="A58">
-        <f t="shared" ref="A58:A63" si="15">C58*100+D58</f>
-        <v>101030506</v>
+        <f>C58*100+D58</f>
+        <v>101030501</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C58" s="3">
         <v>1010305</v>
       </c>
       <c r="D58">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E58" t="str">
-        <f t="shared" ref="E58:E63" si="16">_xlfn.TEXTJOIN("|",TRUE,G58,K58)</f>
-        <v>10000_20020012</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G58,K58)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="F58">
         <v>99999</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" ref="G58:G63" si="17">_xlfn.TEXTJOIN("_",TRUE,H58:I58)</f>
-        <v>10000_20020012</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H58:I58)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="H58">
         <v>10000</v>
       </c>
       <c r="I58">
-        <v>20020012</v>
+        <v>20020020</v>
       </c>
       <c r="J58" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:10">
       <c r="A59">
-        <f t="shared" si="15"/>
-        <v>101030507</v>
+        <f>C59*100+D59</f>
+        <v>101030502</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C59" s="3">
         <v>1010305</v>
       </c>
       <c r="D59">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E59" t="str">
-        <f t="shared" si="16"/>
-        <v>10000_20020012</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G59,K59)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="F59">
         <v>99999</v>
       </c>
       <c r="G59" t="str">
-        <f t="shared" si="17"/>
-        <v>10000_20020012</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H59:I59)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="H59">
         <v>10000</v>
       </c>
       <c r="I59">
-        <v>20020012</v>
+        <v>20020021</v>
       </c>
       <c r="J59" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:10">
       <c r="A60">
-        <f t="shared" si="15"/>
-        <v>101030508</v>
+        <f>C60*100+D60</f>
+        <v>101030503</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C60" s="3">
         <v>1010305</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E60" t="str">
-        <f t="shared" si="16"/>
-        <v>10000_20020012</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G60,K60)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="F60">
         <v>99999</v>
       </c>
       <c r="G60" t="str">
-        <f t="shared" si="17"/>
-        <v>10000_20020012</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H60:I60)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="H60">
         <v>10000</v>
       </c>
       <c r="I60">
-        <v>20020012</v>
+        <v>20020020</v>
       </c>
       <c r="J60" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:10">
       <c r="A61">
-        <f t="shared" si="15"/>
-        <v>101030509</v>
+        <f>C61*100+D61</f>
+        <v>101030504</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C61" s="3">
         <v>1010305</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E61" t="str">
-        <f t="shared" si="16"/>
-        <v>10000_20020013</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G61,K61)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="F61">
         <v>99999</v>
       </c>
       <c r="G61" t="str">
-        <f t="shared" si="17"/>
-        <v>10000_20020013</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H61:I61)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="H61">
         <v>10000</v>
       </c>
       <c r="I61">
-        <v>20020013</v>
+        <v>20020021</v>
       </c>
       <c r="J61" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:10">
       <c r="A62">
-        <f t="shared" si="15"/>
-        <v>101030510</v>
+        <f>C62*100+D62</f>
+        <v>101030505</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C62" s="3">
         <v>1010305</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E62" t="str">
-        <f t="shared" si="16"/>
-        <v>10000_20020004</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G62,K62)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="F62">
         <v>99999</v>
       </c>
       <c r="G62" t="str">
-        <f t="shared" si="17"/>
-        <v>10000_20020004</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H62:I62)</f>
+        <v>10000_20020020</v>
       </c>
       <c r="H62">
         <v>10000</v>
       </c>
       <c r="I62">
-        <v>20020004</v>
+        <v>20020020</v>
       </c>
       <c r="J62" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" spans="1:14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:10">
       <c r="A63">
-        <f t="shared" si="15"/>
-        <v>101030511</v>
+        <f>C63*100+D63</f>
+        <v>101030506</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C63" s="3">
         <v>1010305</v>
       </c>
       <c r="D63">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E63" t="str">
-        <f t="shared" si="16"/>
-        <v>6500_0|3500_20020005</v>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G63,K63)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="F63">
         <v>99999</v>
       </c>
       <c r="G63" t="str">
-        <f t="shared" si="17"/>
-        <v>6500_0</v>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H63:I63)</f>
+        <v>10000_20020021</v>
       </c>
       <c r="H63">
-        <v>6500</v>
+        <v>10000</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>20020021</v>
       </c>
       <c r="J63" t="s">
-        <v>34</v>
-      </c>
-      <c r="K63" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L63:M63)</f>
-        <v>3500_20020005</v>
-      </c>
-      <c r="L63">
-        <v>3500</v>
-      </c>
-      <c r="M63">
-        <v>20020005</v>
-      </c>
-      <c r="N63" t="s">
-        <v>71</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:10">
+      <c r="A64">
+        <f>C64*100+D64</f>
+        <v>101030507</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1010305</v>
+      </c>
+      <c r="D64">
+        <v>7</v>
+      </c>
+      <c r="E64" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G64,K64)</f>
+        <v>10000_20020020</v>
+      </c>
+      <c r="F64">
+        <v>99999</v>
+      </c>
+      <c r="G64" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H64:I64)</f>
+        <v>10000_20020020</v>
+      </c>
+      <c r="H64">
+        <v>10000</v>
+      </c>
+      <c r="I64">
+        <v>20020020</v>
+      </c>
+      <c r="J64" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:10">
+      <c r="A65">
+        <f>C65*100+D65</f>
+        <v>101030508</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1010305</v>
+      </c>
+      <c r="D65">
+        <v>8</v>
+      </c>
+      <c r="E65" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G65,K65)</f>
+        <v>10000_20020021</v>
+      </c>
+      <c r="F65">
+        <v>99999</v>
+      </c>
+      <c r="G65" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H65:I65)</f>
+        <v>10000_20020021</v>
+      </c>
+      <c r="H65">
+        <v>10000</v>
+      </c>
+      <c r="I65">
+        <v>20020021</v>
+      </c>
+      <c r="J65" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:10">
+      <c r="A66">
+        <f>C66*100+D66</f>
+        <v>101030509</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1010305</v>
+      </c>
+      <c r="D66">
+        <v>9</v>
+      </c>
+      <c r="E66" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G66,K66)</f>
+        <v>10000_20020020</v>
+      </c>
+      <c r="F66">
+        <v>99999</v>
+      </c>
+      <c r="G66" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H66:I66)</f>
+        <v>10000_20020020</v>
+      </c>
+      <c r="H66">
+        <v>10000</v>
+      </c>
+      <c r="I66">
+        <v>20020020</v>
+      </c>
+      <c r="J66" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:10">
+      <c r="A67">
+        <f>C67*100+D67</f>
+        <v>101030510</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1010305</v>
+      </c>
+      <c r="D67">
+        <v>10</v>
+      </c>
+      <c r="E67" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G67,K67)</f>
+        <v>10000_20020021</v>
+      </c>
+      <c r="F67">
+        <v>99999</v>
+      </c>
+      <c r="G67" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,H67:I67)</f>
+        <v>10000_20020021</v>
+      </c>
+      <c r="H67">
+        <v>10000</v>
+      </c>
+      <c r="I67">
+        <v>20020021</v>
+      </c>
+      <c r="J67" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/dropGroup.xlsx
+++ b/poker/resources/sample/dropGroup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="dropGroup" sheetId="1" r:id="rId1"/>
@@ -1917,17 +1917,18 @@
       </c>
       <c r="E26" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,G26,K26)</f>
-        <v>7250_0|2750_20010040</v>
+        <v>1750_0|8250_20010040</v>
       </c>
       <c r="F26">
         <v>99999</v>
       </c>
       <c r="G26" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,H26:I26)</f>
-        <v>7250_0</v>
+        <v>1750_0</v>
       </c>
       <c r="H26">
-        <v>7250</v>
+        <f>10000-L26</f>
+        <v>1750</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1937,11 +1938,10 @@
       </c>
       <c r="K26" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,L26:M26)</f>
-        <v>2750_20010040</v>
+        <v>8250_20010040</v>
       </c>
       <c r="L26">
-        <f>10000-H26</f>
-        <v>2750</v>
+        <v>8250</v>
       </c>
       <c r="M26">
         <v>20010040</v>
@@ -1962,17 +1962,18 @@
       </c>
       <c r="E27" t="str">
         <f t="shared" ref="E27:E43" si="0">_xlfn.TEXTJOIN("|",TRUE,G27,K27)</f>
-        <v>7226_0|2774_20010050</v>
+        <v>1678_0|8322_20010050</v>
       </c>
       <c r="F27">
         <v>99999</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" ref="G27:G49" si="1">_xlfn.TEXTJOIN("_",TRUE,H27:I27)</f>
-        <v>7226_0</v>
+        <f t="shared" ref="G27:G51" si="1">_xlfn.TEXTJOIN("_",TRUE,H27:I27)</f>
+        <v>1678_0</v>
       </c>
       <c r="H27">
-        <v>7226</v>
+        <f t="shared" ref="H27:H37" si="2">10000-L27</f>
+        <v>1678</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1981,12 +1982,11 @@
         <v>34</v>
       </c>
       <c r="K27" t="str">
-        <f t="shared" ref="K27:K37" si="2">_xlfn.TEXTJOIN("_",TRUE,L27:M27)</f>
-        <v>2774_20010050</v>
+        <f t="shared" ref="K27:K37" si="3">_xlfn.TEXTJOIN("_",TRUE,L27:M27)</f>
+        <v>8322_20010050</v>
       </c>
       <c r="L27">
-        <f t="shared" ref="L27:L37" si="3">10000-H27</f>
-        <v>2774</v>
+        <v>8322</v>
       </c>
       <c r="M27">
         <v>20010050</v>
@@ -2007,17 +2007,18 @@
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
-        <v>6588_0|3412_20010060</v>
+        <v>1500_0|8500_20010060</v>
       </c>
       <c r="F28">
         <v>99999</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="1"/>
-        <v>6588_0</v>
+        <v>1500_0</v>
       </c>
       <c r="H28">
-        <v>6588</v>
+        <f t="shared" si="2"/>
+        <v>1500</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2026,12 +2027,11 @@
         <v>34</v>
       </c>
       <c r="K28" t="str">
-        <f t="shared" si="2"/>
-        <v>3412_20010060</v>
+        <f t="shared" si="3"/>
+        <v>8500_20010060</v>
       </c>
       <c r="L28">
-        <f t="shared" si="3"/>
-        <v>3412</v>
+        <v>8500</v>
       </c>
       <c r="M28">
         <v>20010060</v>
@@ -2052,17 +2052,18 @@
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
-        <v>7788_0|2212_20010070</v>
+        <v>2500_0|7500_20010070</v>
       </c>
       <c r="F29">
         <v>99999</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="1"/>
-        <v>7788_0</v>
+        <v>2500_0</v>
       </c>
       <c r="H29">
-        <v>7788</v>
+        <f t="shared" si="2"/>
+        <v>2500</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2071,12 +2072,11 @@
         <v>34</v>
       </c>
       <c r="K29" t="str">
-        <f t="shared" si="2"/>
-        <v>2212_20010070</v>
+        <f t="shared" si="3"/>
+        <v>7500_20010070</v>
       </c>
       <c r="L29">
-        <f t="shared" si="3"/>
-        <v>2212</v>
+        <v>7500</v>
       </c>
       <c r="M29">
         <v>20010070</v>
@@ -2097,17 +2097,18 @@
       </c>
       <c r="E30" t="str">
         <f t="shared" si="0"/>
-        <v>6951_0|3049_20010080</v>
+        <v>853_0|9147_20010080</v>
       </c>
       <c r="F30">
         <v>99999</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="1"/>
-        <v>6951_0</v>
+        <v>853_0</v>
       </c>
       <c r="H30">
-        <v>6951</v>
+        <f t="shared" si="2"/>
+        <v>853</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2116,12 +2117,11 @@
         <v>34</v>
       </c>
       <c r="K30" t="str">
-        <f t="shared" si="2"/>
-        <v>3049_20010080</v>
+        <f t="shared" si="3"/>
+        <v>9147_20010080</v>
       </c>
       <c r="L30">
-        <f t="shared" si="3"/>
-        <v>3049</v>
+        <v>9147</v>
       </c>
       <c r="M30">
         <v>20010080</v>
@@ -2142,17 +2142,18 @@
       </c>
       <c r="E31" t="str">
         <f t="shared" si="0"/>
-        <v>7861_0|2139_20010090</v>
+        <v>3583_0|6417_20010090</v>
       </c>
       <c r="F31">
         <v>99999</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="1"/>
-        <v>7861_0</v>
+        <v>3583_0</v>
       </c>
       <c r="H31">
-        <v>7861</v>
+        <f t="shared" si="2"/>
+        <v>3583</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2161,12 +2162,11 @@
         <v>34</v>
       </c>
       <c r="K31" t="str">
-        <f t="shared" si="2"/>
-        <v>2139_20010090</v>
+        <f t="shared" si="3"/>
+        <v>6417_20010090</v>
       </c>
       <c r="L31">
-        <f t="shared" si="3"/>
-        <v>2139</v>
+        <v>6417</v>
       </c>
       <c r="M31">
         <v>20010090</v>
@@ -2187,17 +2187,18 @@
       </c>
       <c r="E32" t="str">
         <f t="shared" si="0"/>
-        <v>7826_0|2174_20010100</v>
+        <v>3478_0|6522_20010100</v>
       </c>
       <c r="F32">
         <v>99999</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="1"/>
-        <v>7826_0</v>
+        <v>3478_0</v>
       </c>
       <c r="H32">
-        <v>7826</v>
+        <f t="shared" si="2"/>
+        <v>3478</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2206,12 +2207,11 @@
         <v>34</v>
       </c>
       <c r="K32" t="str">
-        <f t="shared" si="2"/>
-        <v>2174_20010100</v>
+        <f t="shared" si="3"/>
+        <v>6522_20010100</v>
       </c>
       <c r="L32">
-        <f t="shared" si="3"/>
-        <v>2174</v>
+        <v>6522</v>
       </c>
       <c r="M32">
         <v>20010100</v>
@@ -2232,17 +2232,18 @@
       </c>
       <c r="E33" t="str">
         <f t="shared" si="0"/>
-        <v>7858_0|2142_20010110</v>
+        <v>3574_0|6426_20010110</v>
       </c>
       <c r="F33">
         <v>99999</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
-        <v>7858_0</v>
+        <v>3574_0</v>
       </c>
       <c r="H33">
-        <v>7858</v>
+        <f t="shared" si="2"/>
+        <v>3574</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2251,12 +2252,11 @@
         <v>34</v>
       </c>
       <c r="K33" t="str">
-        <f t="shared" si="2"/>
-        <v>2142_20010110</v>
+        <f t="shared" si="3"/>
+        <v>6426_20010110</v>
       </c>
       <c r="L33">
-        <f t="shared" si="3"/>
-        <v>2142</v>
+        <v>6426</v>
       </c>
       <c r="M33">
         <v>20010110</v>
@@ -2277,17 +2277,18 @@
       </c>
       <c r="E34" t="str">
         <f t="shared" si="0"/>
-        <v>7779_0|2221_20010120</v>
+        <v>3337_0|6663_20010120</v>
       </c>
       <c r="F34">
         <v>99999</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="1"/>
-        <v>7779_0</v>
+        <v>3337_0</v>
       </c>
       <c r="H34">
-        <v>7779</v>
+        <f t="shared" si="2"/>
+        <v>3337</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2296,12 +2297,11 @@
         <v>34</v>
       </c>
       <c r="K34" t="str">
-        <f t="shared" si="2"/>
-        <v>2221_20010120</v>
+        <f t="shared" si="3"/>
+        <v>6663_20010120</v>
       </c>
       <c r="L34">
-        <f t="shared" si="3"/>
-        <v>2221</v>
+        <v>6663</v>
       </c>
       <c r="M34">
         <v>20010120</v>
@@ -2322,17 +2322,18 @@
       </c>
       <c r="E35" t="str">
         <f t="shared" si="0"/>
-        <v>7828_0|2172_20010130</v>
+        <v>3484_0|6516_20010130</v>
       </c>
       <c r="F35">
         <v>99999</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="1"/>
-        <v>7828_0</v>
+        <v>3484_0</v>
       </c>
       <c r="H35">
-        <v>7828</v>
+        <f t="shared" si="2"/>
+        <v>3484</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2341,12 +2342,11 @@
         <v>34</v>
       </c>
       <c r="K35" t="str">
-        <f t="shared" si="2"/>
-        <v>2172_20010130</v>
+        <f t="shared" si="3"/>
+        <v>6516_20010130</v>
       </c>
       <c r="L35">
-        <f t="shared" si="3"/>
-        <v>2172</v>
+        <v>6516</v>
       </c>
       <c r="M35">
         <v>20010130</v>
@@ -2367,17 +2367,18 @@
       </c>
       <c r="E36" t="str">
         <f t="shared" si="0"/>
-        <v>8677_0|1323_20010140</v>
+        <v>6031_0|3969_20010140</v>
       </c>
       <c r="F36">
         <v>99999</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="1"/>
-        <v>8677_0</v>
+        <v>6031_0</v>
       </c>
       <c r="H36">
-        <v>8677</v>
+        <f t="shared" si="2"/>
+        <v>6031</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2386,12 +2387,11 @@
         <v>34</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" si="2"/>
-        <v>1323_20010140</v>
+        <f t="shared" si="3"/>
+        <v>3969_20010140</v>
       </c>
       <c r="L36">
-        <f t="shared" si="3"/>
-        <v>1323</v>
+        <v>3969</v>
       </c>
       <c r="M36">
         <v>20010140</v>
@@ -2412,17 +2412,18 @@
       </c>
       <c r="E37" t="str">
         <f t="shared" si="0"/>
-        <v>8981_0|1019_20010150</v>
+        <v>6943_0|3057_20010150</v>
       </c>
       <c r="F37">
         <v>99999</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="1"/>
-        <v>8981_0</v>
+        <v>6943_0</v>
       </c>
       <c r="H37">
-        <v>8981</v>
+        <f t="shared" si="2"/>
+        <v>6943</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2431,12 +2432,11 @@
         <v>34</v>
       </c>
       <c r="K37" t="str">
-        <f t="shared" si="2"/>
-        <v>1019_20010150</v>
+        <f t="shared" si="3"/>
+        <v>3057_20010150</v>
       </c>
       <c r="L37">
-        <f t="shared" si="3"/>
-        <v>1019</v>
+        <v>3057</v>
       </c>
       <c r="M37">
         <v>20010150</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="44" customFormat="1" spans="1:14">
       <c r="A44">
-        <f t="shared" ref="A44:A49" si="5">C44*100+D44</f>
+        <f t="shared" ref="A44:A51" si="5">C44*100+D44</f>
         <v>101030301</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -2670,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="str">
-        <f t="shared" ref="E44:E49" si="6">_xlfn.TEXTJOIN("|",TRUE,G44,K44)</f>
+        <f t="shared" ref="E44:E51" si="6">_xlfn.TEXTJOIN("|",TRUE,G44,K44)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F44">
@@ -2867,7 +2867,7 @@
     </row>
     <row r="50" customFormat="1" spans="1:10">
       <c r="A50">
-        <f>C50*100+D50</f>
+        <f t="shared" si="5"/>
         <v>101030401</v>
       </c>
       <c r="B50" s="7" t="s">
@@ -2880,14 +2880,14 @@
         <v>1</v>
       </c>
       <c r="E50" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G50,K50)</f>
+        <f t="shared" si="6"/>
         <v>10000_20020020</v>
       </c>
       <c r="F50">
         <v>99999</v>
       </c>
       <c r="G50" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H50:I50)</f>
+        <f t="shared" si="1"/>
         <v>10000_20020020</v>
       </c>
       <c r="H50">
@@ -2902,7 +2902,7 @@
     </row>
     <row r="51" customFormat="1" spans="1:10">
       <c r="A51">
-        <f>C51*100+D51</f>
+        <f t="shared" si="5"/>
         <v>101030402</v>
       </c>
       <c r="B51" s="7" t="s">
@@ -2915,14 +2915,14 @@
         <v>2</v>
       </c>
       <c r="E51" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G51,K51)</f>
+        <f t="shared" si="6"/>
         <v>10000_20020021</v>
       </c>
       <c r="F51">
         <v>99999</v>
       </c>
       <c r="G51" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H51:I51)</f>
+        <f t="shared" si="1"/>
         <v>10000_20020021</v>
       </c>
       <c r="H51">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="52" customFormat="1" spans="1:10">
       <c r="A52">
-        <f t="shared" ref="A52:A57" si="7">C52*100+D52</f>
+        <f t="shared" ref="A52:A67" si="7">C52*100+D52</f>
         <v>101030403</v>
       </c>
       <c r="B52" s="7" t="s">
@@ -2950,14 +2950,14 @@
         <v>3</v>
       </c>
       <c r="E52" t="str">
-        <f t="shared" ref="E52:E57" si="8">_xlfn.TEXTJOIN("|",TRUE,G52,K52)</f>
+        <f t="shared" ref="E52:E67" si="8">_xlfn.TEXTJOIN("|",TRUE,G52,K52)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F52">
         <v>99999</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" ref="G52:G57" si="9">_xlfn.TEXTJOIN("_",TRUE,H52:I52)</f>
+        <f t="shared" ref="G52:G67" si="9">_xlfn.TEXTJOIN("_",TRUE,H52:I52)</f>
         <v>10000_20020020</v>
       </c>
       <c r="H52">
@@ -3147,7 +3147,7 @@
     </row>
     <row r="58" customFormat="1" spans="1:10">
       <c r="A58">
-        <f>C58*100+D58</f>
+        <f t="shared" si="7"/>
         <v>101030501</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -3160,14 +3160,14 @@
         <v>1</v>
       </c>
       <c r="E58" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G58,K58)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020020</v>
       </c>
       <c r="F58">
         <v>99999</v>
       </c>
       <c r="G58" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H58:I58)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020020</v>
       </c>
       <c r="H58">
@@ -3182,7 +3182,7 @@
     </row>
     <row r="59" customFormat="1" spans="1:10">
       <c r="A59">
-        <f>C59*100+D59</f>
+        <f t="shared" si="7"/>
         <v>101030502</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -3195,14 +3195,14 @@
         <v>2</v>
       </c>
       <c r="E59" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G59,K59)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020021</v>
       </c>
       <c r="F59">
         <v>99999</v>
       </c>
       <c r="G59" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H59:I59)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020021</v>
       </c>
       <c r="H59">
@@ -3217,7 +3217,7 @@
     </row>
     <row r="60" customFormat="1" spans="1:10">
       <c r="A60">
-        <f>C60*100+D60</f>
+        <f t="shared" si="7"/>
         <v>101030503</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -3230,14 +3230,14 @@
         <v>3</v>
       </c>
       <c r="E60" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G60,K60)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020020</v>
       </c>
       <c r="F60">
         <v>99999</v>
       </c>
       <c r="G60" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H60:I60)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020020</v>
       </c>
       <c r="H60">
@@ -3252,7 +3252,7 @@
     </row>
     <row r="61" customFormat="1" spans="1:10">
       <c r="A61">
-        <f>C61*100+D61</f>
+        <f t="shared" si="7"/>
         <v>101030504</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -3265,14 +3265,14 @@
         <v>4</v>
       </c>
       <c r="E61" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G61,K61)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020021</v>
       </c>
       <c r="F61">
         <v>99999</v>
       </c>
       <c r="G61" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H61:I61)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020021</v>
       </c>
       <c r="H61">
@@ -3287,7 +3287,7 @@
     </row>
     <row r="62" customFormat="1" spans="1:10">
       <c r="A62">
-        <f>C62*100+D62</f>
+        <f t="shared" si="7"/>
         <v>101030505</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -3300,14 +3300,14 @@
         <v>5</v>
       </c>
       <c r="E62" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G62,K62)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020020</v>
       </c>
       <c r="F62">
         <v>99999</v>
       </c>
       <c r="G62" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H62:I62)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020020</v>
       </c>
       <c r="H62">
@@ -3322,7 +3322,7 @@
     </row>
     <row r="63" customFormat="1" spans="1:10">
       <c r="A63">
-        <f>C63*100+D63</f>
+        <f t="shared" si="7"/>
         <v>101030506</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -3335,14 +3335,14 @@
         <v>6</v>
       </c>
       <c r="E63" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G63,K63)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020021</v>
       </c>
       <c r="F63">
         <v>99999</v>
       </c>
       <c r="G63" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H63:I63)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020021</v>
       </c>
       <c r="H63">
@@ -3357,7 +3357,7 @@
     </row>
     <row r="64" customFormat="1" spans="1:10">
       <c r="A64">
-        <f>C64*100+D64</f>
+        <f t="shared" si="7"/>
         <v>101030507</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -3370,14 +3370,14 @@
         <v>7</v>
       </c>
       <c r="E64" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G64,K64)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020020</v>
       </c>
       <c r="F64">
         <v>99999</v>
       </c>
       <c r="G64" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H64:I64)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020020</v>
       </c>
       <c r="H64">
@@ -3392,7 +3392,7 @@
     </row>
     <row r="65" customFormat="1" spans="1:10">
       <c r="A65">
-        <f>C65*100+D65</f>
+        <f t="shared" si="7"/>
         <v>101030508</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -3405,14 +3405,14 @@
         <v>8</v>
       </c>
       <c r="E65" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G65,K65)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020021</v>
       </c>
       <c r="F65">
         <v>99999</v>
       </c>
       <c r="G65" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H65:I65)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020021</v>
       </c>
       <c r="H65">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="66" customFormat="1" spans="1:10">
       <c r="A66">
-        <f>C66*100+D66</f>
+        <f t="shared" si="7"/>
         <v>101030509</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -3440,14 +3440,14 @@
         <v>9</v>
       </c>
       <c r="E66" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G66,K66)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020020</v>
       </c>
       <c r="F66">
         <v>99999</v>
       </c>
       <c r="G66" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H66:I66)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020020</v>
       </c>
       <c r="H66">
@@ -3462,7 +3462,7 @@
     </row>
     <row r="67" customFormat="1" spans="1:10">
       <c r="A67">
-        <f>C67*100+D67</f>
+        <f t="shared" si="7"/>
         <v>101030510</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -3475,14 +3475,14 @@
         <v>10</v>
       </c>
       <c r="E67" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,G67,K67)</f>
+        <f t="shared" si="8"/>
         <v>10000_20020021</v>
       </c>
       <c r="F67">
         <v>99999</v>
       </c>
       <c r="G67" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,H67:I67)</f>
+        <f t="shared" si="9"/>
         <v>10000_20020021</v>
       </c>
       <c r="H67">

--- a/poker/resources/sample/dropGroup.xlsx
+++ b/poker/resources/sample/dropGroup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="dropGroup" sheetId="1" r:id="rId1"/>
@@ -1917,18 +1917,17 @@
       </c>
       <c r="E26" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,G26,K26)</f>
-        <v>1750_0|8250_20010040</v>
+        <v>7250_0|2750_20010040</v>
       </c>
       <c r="F26">
         <v>99999</v>
       </c>
       <c r="G26" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,H26:I26)</f>
-        <v>1750_0</v>
+        <v>7250_0</v>
       </c>
       <c r="H26">
-        <f>10000-L26</f>
-        <v>1750</v>
+        <v>7250</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1938,10 +1937,11 @@
       </c>
       <c r="K26" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,L26:M26)</f>
-        <v>8250_20010040</v>
+        <v>2750_20010040</v>
       </c>
       <c r="L26">
-        <v>8250</v>
+        <f>10000-H26</f>
+        <v>2750</v>
       </c>
       <c r="M26">
         <v>20010040</v>
@@ -1962,18 +1962,17 @@
       </c>
       <c r="E27" t="str">
         <f t="shared" ref="E27:E43" si="0">_xlfn.TEXTJOIN("|",TRUE,G27,K27)</f>
-        <v>1678_0|8322_20010050</v>
+        <v>7226_0|2774_20010050</v>
       </c>
       <c r="F27">
         <v>99999</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" ref="G27:G51" si="1">_xlfn.TEXTJOIN("_",TRUE,H27:I27)</f>
-        <v>1678_0</v>
+        <f t="shared" ref="G27:G49" si="1">_xlfn.TEXTJOIN("_",TRUE,H27:I27)</f>
+        <v>7226_0</v>
       </c>
       <c r="H27">
-        <f t="shared" ref="H27:H37" si="2">10000-L27</f>
-        <v>1678</v>
+        <v>7226</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1982,11 +1981,12 @@
         <v>34</v>
       </c>
       <c r="K27" t="str">
-        <f t="shared" ref="K27:K37" si="3">_xlfn.TEXTJOIN("_",TRUE,L27:M27)</f>
-        <v>8322_20010050</v>
+        <f t="shared" ref="K27:K37" si="2">_xlfn.TEXTJOIN("_",TRUE,L27:M27)</f>
+        <v>2774_20010050</v>
       </c>
       <c r="L27">
-        <v>8322</v>
+        <f t="shared" ref="L27:L37" si="3">10000-H27</f>
+        <v>2774</v>
       </c>
       <c r="M27">
         <v>20010050</v>
@@ -2007,18 +2007,17 @@
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
-        <v>1500_0|8500_20010060</v>
+        <v>6588_0|3412_20010060</v>
       </c>
       <c r="F28">
         <v>99999</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="1"/>
-        <v>1500_0</v>
+        <v>6588_0</v>
       </c>
       <c r="H28">
-        <f t="shared" si="2"/>
-        <v>1500</v>
+        <v>6588</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2027,11 +2026,12 @@
         <v>34</v>
       </c>
       <c r="K28" t="str">
+        <f t="shared" si="2"/>
+        <v>3412_20010060</v>
+      </c>
+      <c r="L28">
         <f t="shared" si="3"/>
-        <v>8500_20010060</v>
-      </c>
-      <c r="L28">
-        <v>8500</v>
+        <v>3412</v>
       </c>
       <c r="M28">
         <v>20010060</v>
@@ -2052,18 +2052,17 @@
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
-        <v>2500_0|7500_20010070</v>
+        <v>7788_0|2212_20010070</v>
       </c>
       <c r="F29">
         <v>99999</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="1"/>
-        <v>2500_0</v>
+        <v>7788_0</v>
       </c>
       <c r="H29">
-        <f t="shared" si="2"/>
-        <v>2500</v>
+        <v>7788</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2072,11 +2071,12 @@
         <v>34</v>
       </c>
       <c r="K29" t="str">
+        <f t="shared" si="2"/>
+        <v>2212_20010070</v>
+      </c>
+      <c r="L29">
         <f t="shared" si="3"/>
-        <v>7500_20010070</v>
-      </c>
-      <c r="L29">
-        <v>7500</v>
+        <v>2212</v>
       </c>
       <c r="M29">
         <v>20010070</v>
@@ -2097,18 +2097,17 @@
       </c>
       <c r="E30" t="str">
         <f t="shared" si="0"/>
-        <v>853_0|9147_20010080</v>
+        <v>6951_0|3049_20010080</v>
       </c>
       <c r="F30">
         <v>99999</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="1"/>
-        <v>853_0</v>
+        <v>6951_0</v>
       </c>
       <c r="H30">
-        <f t="shared" si="2"/>
-        <v>853</v>
+        <v>6951</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2117,11 +2116,12 @@
         <v>34</v>
       </c>
       <c r="K30" t="str">
+        <f t="shared" si="2"/>
+        <v>3049_20010080</v>
+      </c>
+      <c r="L30">
         <f t="shared" si="3"/>
-        <v>9147_20010080</v>
-      </c>
-      <c r="L30">
-        <v>9147</v>
+        <v>3049</v>
       </c>
       <c r="M30">
         <v>20010080</v>
@@ -2142,18 +2142,17 @@
       </c>
       <c r="E31" t="str">
         <f t="shared" si="0"/>
-        <v>3583_0|6417_20010090</v>
+        <v>7861_0|2139_20010090</v>
       </c>
       <c r="F31">
         <v>99999</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="1"/>
-        <v>3583_0</v>
+        <v>7861_0</v>
       </c>
       <c r="H31">
-        <f t="shared" si="2"/>
-        <v>3583</v>
+        <v>7861</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2162,11 +2161,12 @@
         <v>34</v>
       </c>
       <c r="K31" t="str">
+        <f t="shared" si="2"/>
+        <v>2139_20010090</v>
+      </c>
+      <c r="L31">
         <f t="shared" si="3"/>
-        <v>6417_20010090</v>
-      </c>
-      <c r="L31">
-        <v>6417</v>
+        <v>2139</v>
       </c>
       <c r="M31">
         <v>20010090</v>
@@ -2187,18 +2187,17 @@
       </c>
       <c r="E32" t="str">
         <f t="shared" si="0"/>
-        <v>3478_0|6522_20010100</v>
+        <v>7826_0|2174_20010100</v>
       </c>
       <c r="F32">
         <v>99999</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="1"/>
-        <v>3478_0</v>
+        <v>7826_0</v>
       </c>
       <c r="H32">
-        <f t="shared" si="2"/>
-        <v>3478</v>
+        <v>7826</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2207,11 +2206,12 @@
         <v>34</v>
       </c>
       <c r="K32" t="str">
+        <f t="shared" si="2"/>
+        <v>2174_20010100</v>
+      </c>
+      <c r="L32">
         <f t="shared" si="3"/>
-        <v>6522_20010100</v>
-      </c>
-      <c r="L32">
-        <v>6522</v>
+        <v>2174</v>
       </c>
       <c r="M32">
         <v>20010100</v>
@@ -2232,18 +2232,17 @@
       </c>
       <c r="E33" t="str">
         <f t="shared" si="0"/>
-        <v>3574_0|6426_20010110</v>
+        <v>7858_0|2142_20010110</v>
       </c>
       <c r="F33">
         <v>99999</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
-        <v>3574_0</v>
+        <v>7858_0</v>
       </c>
       <c r="H33">
-        <f t="shared" si="2"/>
-        <v>3574</v>
+        <v>7858</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2252,11 +2251,12 @@
         <v>34</v>
       </c>
       <c r="K33" t="str">
+        <f t="shared" si="2"/>
+        <v>2142_20010110</v>
+      </c>
+      <c r="L33">
         <f t="shared" si="3"/>
-        <v>6426_20010110</v>
-      </c>
-      <c r="L33">
-        <v>6426</v>
+        <v>2142</v>
       </c>
       <c r="M33">
         <v>20010110</v>
@@ -2277,18 +2277,17 @@
       </c>
       <c r="E34" t="str">
         <f t="shared" si="0"/>
-        <v>3337_0|6663_20010120</v>
+        <v>7779_0|2221_20010120</v>
       </c>
       <c r="F34">
         <v>99999</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="1"/>
-        <v>3337_0</v>
+        <v>7779_0</v>
       </c>
       <c r="H34">
-        <f t="shared" si="2"/>
-        <v>3337</v>
+        <v>7779</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2297,11 +2296,12 @@
         <v>34</v>
       </c>
       <c r="K34" t="str">
+        <f t="shared" si="2"/>
+        <v>2221_20010120</v>
+      </c>
+      <c r="L34">
         <f t="shared" si="3"/>
-        <v>6663_20010120</v>
-      </c>
-      <c r="L34">
-        <v>6663</v>
+        <v>2221</v>
       </c>
       <c r="M34">
         <v>20010120</v>
@@ -2322,18 +2322,17 @@
       </c>
       <c r="E35" t="str">
         <f t="shared" si="0"/>
-        <v>3484_0|6516_20010130</v>
+        <v>7828_0|2172_20010130</v>
       </c>
       <c r="F35">
         <v>99999</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="1"/>
-        <v>3484_0</v>
+        <v>7828_0</v>
       </c>
       <c r="H35">
-        <f t="shared" si="2"/>
-        <v>3484</v>
+        <v>7828</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2342,11 +2341,12 @@
         <v>34</v>
       </c>
       <c r="K35" t="str">
+        <f t="shared" si="2"/>
+        <v>2172_20010130</v>
+      </c>
+      <c r="L35">
         <f t="shared" si="3"/>
-        <v>6516_20010130</v>
-      </c>
-      <c r="L35">
-        <v>6516</v>
+        <v>2172</v>
       </c>
       <c r="M35">
         <v>20010130</v>
@@ -2367,18 +2367,17 @@
       </c>
       <c r="E36" t="str">
         <f t="shared" si="0"/>
-        <v>6031_0|3969_20010140</v>
+        <v>8677_0|1323_20010140</v>
       </c>
       <c r="F36">
         <v>99999</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="1"/>
-        <v>6031_0</v>
+        <v>8677_0</v>
       </c>
       <c r="H36">
-        <f t="shared" si="2"/>
-        <v>6031</v>
+        <v>8677</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2387,11 +2386,12 @@
         <v>34</v>
       </c>
       <c r="K36" t="str">
+        <f t="shared" si="2"/>
+        <v>1323_20010140</v>
+      </c>
+      <c r="L36">
         <f t="shared" si="3"/>
-        <v>3969_20010140</v>
-      </c>
-      <c r="L36">
-        <v>3969</v>
+        <v>1323</v>
       </c>
       <c r="M36">
         <v>20010140</v>
@@ -2412,18 +2412,17 @@
       </c>
       <c r="E37" t="str">
         <f t="shared" si="0"/>
-        <v>6943_0|3057_20010150</v>
+        <v>8981_0|1019_20010150</v>
       </c>
       <c r="F37">
         <v>99999</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="1"/>
-        <v>6943_0</v>
+        <v>8981_0</v>
       </c>
       <c r="H37">
-        <f t="shared" si="2"/>
-        <v>6943</v>
+        <v>8981</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2432,11 +2431,12 @@
         <v>34</v>
       </c>
       <c r="K37" t="str">
+        <f t="shared" si="2"/>
+        <v>1019_20010150</v>
+      </c>
+      <c r="L37">
         <f t="shared" si="3"/>
-        <v>3057_20010150</v>
-      </c>
-      <c r="L37">
-        <v>3057</v>
+        <v>1019</v>
       </c>
       <c r="M37">
         <v>20010150</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="44" customFormat="1" spans="1:14">
       <c r="A44">
-        <f t="shared" ref="A44:A51" si="5">C44*100+D44</f>
+        <f t="shared" ref="A44:A49" si="5">C44*100+D44</f>
         <v>101030301</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -2670,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="str">
-        <f t="shared" ref="E44:E51" si="6">_xlfn.TEXTJOIN("|",TRUE,G44,K44)</f>
+        <f t="shared" ref="E44:E49" si="6">_xlfn.TEXTJOIN("|",TRUE,G44,K44)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F44">
@@ -2867,7 +2867,7 @@
     </row>
     <row r="50" customFormat="1" spans="1:10">
       <c r="A50">
-        <f t="shared" si="5"/>
+        <f>C50*100+D50</f>
         <v>101030401</v>
       </c>
       <c r="B50" s="7" t="s">
@@ -2880,14 +2880,14 @@
         <v>1</v>
       </c>
       <c r="E50" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G50,K50)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F50">
         <v>99999</v>
       </c>
       <c r="G50" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H50:I50)</f>
         <v>10000_20020020</v>
       </c>
       <c r="H50">
@@ -2902,7 +2902,7 @@
     </row>
     <row r="51" customFormat="1" spans="1:10">
       <c r="A51">
-        <f t="shared" si="5"/>
+        <f>C51*100+D51</f>
         <v>101030402</v>
       </c>
       <c r="B51" s="7" t="s">
@@ -2915,14 +2915,14 @@
         <v>2</v>
       </c>
       <c r="E51" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G51,K51)</f>
         <v>10000_20020021</v>
       </c>
       <c r="F51">
         <v>99999</v>
       </c>
       <c r="G51" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H51:I51)</f>
         <v>10000_20020021</v>
       </c>
       <c r="H51">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="52" customFormat="1" spans="1:10">
       <c r="A52">
-        <f t="shared" ref="A52:A67" si="7">C52*100+D52</f>
+        <f t="shared" ref="A52:A57" si="7">C52*100+D52</f>
         <v>101030403</v>
       </c>
       <c r="B52" s="7" t="s">
@@ -2950,14 +2950,14 @@
         <v>3</v>
       </c>
       <c r="E52" t="str">
-        <f t="shared" ref="E52:E67" si="8">_xlfn.TEXTJOIN("|",TRUE,G52,K52)</f>
+        <f t="shared" ref="E52:E57" si="8">_xlfn.TEXTJOIN("|",TRUE,G52,K52)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F52">
         <v>99999</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" ref="G52:G67" si="9">_xlfn.TEXTJOIN("_",TRUE,H52:I52)</f>
+        <f t="shared" ref="G52:G57" si="9">_xlfn.TEXTJOIN("_",TRUE,H52:I52)</f>
         <v>10000_20020020</v>
       </c>
       <c r="H52">
@@ -3147,7 +3147,7 @@
     </row>
     <row r="58" customFormat="1" spans="1:10">
       <c r="A58">
-        <f t="shared" si="7"/>
+        <f>C58*100+D58</f>
         <v>101030501</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -3160,14 +3160,14 @@
         <v>1</v>
       </c>
       <c r="E58" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G58,K58)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F58">
         <v>99999</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H58:I58)</f>
         <v>10000_20020020</v>
       </c>
       <c r="H58">
@@ -3182,7 +3182,7 @@
     </row>
     <row r="59" customFormat="1" spans="1:10">
       <c r="A59">
-        <f t="shared" si="7"/>
+        <f>C59*100+D59</f>
         <v>101030502</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -3195,14 +3195,14 @@
         <v>2</v>
       </c>
       <c r="E59" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G59,K59)</f>
         <v>10000_20020021</v>
       </c>
       <c r="F59">
         <v>99999</v>
       </c>
       <c r="G59" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H59:I59)</f>
         <v>10000_20020021</v>
       </c>
       <c r="H59">
@@ -3217,7 +3217,7 @@
     </row>
     <row r="60" customFormat="1" spans="1:10">
       <c r="A60">
-        <f t="shared" si="7"/>
+        <f>C60*100+D60</f>
         <v>101030503</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -3230,14 +3230,14 @@
         <v>3</v>
       </c>
       <c r="E60" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G60,K60)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F60">
         <v>99999</v>
       </c>
       <c r="G60" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H60:I60)</f>
         <v>10000_20020020</v>
       </c>
       <c r="H60">
@@ -3252,7 +3252,7 @@
     </row>
     <row r="61" customFormat="1" spans="1:10">
       <c r="A61">
-        <f t="shared" si="7"/>
+        <f>C61*100+D61</f>
         <v>101030504</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -3265,14 +3265,14 @@
         <v>4</v>
       </c>
       <c r="E61" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G61,K61)</f>
         <v>10000_20020021</v>
       </c>
       <c r="F61">
         <v>99999</v>
       </c>
       <c r="G61" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H61:I61)</f>
         <v>10000_20020021</v>
       </c>
       <c r="H61">
@@ -3287,7 +3287,7 @@
     </row>
     <row r="62" customFormat="1" spans="1:10">
       <c r="A62">
-        <f t="shared" si="7"/>
+        <f>C62*100+D62</f>
         <v>101030505</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -3300,14 +3300,14 @@
         <v>5</v>
       </c>
       <c r="E62" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G62,K62)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F62">
         <v>99999</v>
       </c>
       <c r="G62" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H62:I62)</f>
         <v>10000_20020020</v>
       </c>
       <c r="H62">
@@ -3322,7 +3322,7 @@
     </row>
     <row r="63" customFormat="1" spans="1:10">
       <c r="A63">
-        <f t="shared" si="7"/>
+        <f>C63*100+D63</f>
         <v>101030506</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -3335,14 +3335,14 @@
         <v>6</v>
       </c>
       <c r="E63" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G63,K63)</f>
         <v>10000_20020021</v>
       </c>
       <c r="F63">
         <v>99999</v>
       </c>
       <c r="G63" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H63:I63)</f>
         <v>10000_20020021</v>
       </c>
       <c r="H63">
@@ -3357,7 +3357,7 @@
     </row>
     <row r="64" customFormat="1" spans="1:10">
       <c r="A64">
-        <f t="shared" si="7"/>
+        <f>C64*100+D64</f>
         <v>101030507</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -3370,14 +3370,14 @@
         <v>7</v>
       </c>
       <c r="E64" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G64,K64)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F64">
         <v>99999</v>
       </c>
       <c r="G64" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H64:I64)</f>
         <v>10000_20020020</v>
       </c>
       <c r="H64">
@@ -3392,7 +3392,7 @@
     </row>
     <row r="65" customFormat="1" spans="1:10">
       <c r="A65">
-        <f t="shared" si="7"/>
+        <f>C65*100+D65</f>
         <v>101030508</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -3405,14 +3405,14 @@
         <v>8</v>
       </c>
       <c r="E65" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G65,K65)</f>
         <v>10000_20020021</v>
       </c>
       <c r="F65">
         <v>99999</v>
       </c>
       <c r="G65" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H65:I65)</f>
         <v>10000_20020021</v>
       </c>
       <c r="H65">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="66" customFormat="1" spans="1:10">
       <c r="A66">
-        <f t="shared" si="7"/>
+        <f>C66*100+D66</f>
         <v>101030509</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -3440,14 +3440,14 @@
         <v>9</v>
       </c>
       <c r="E66" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G66,K66)</f>
         <v>10000_20020020</v>
       </c>
       <c r="F66">
         <v>99999</v>
       </c>
       <c r="G66" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H66:I66)</f>
         <v>10000_20020020</v>
       </c>
       <c r="H66">
@@ -3462,7 +3462,7 @@
     </row>
     <row r="67" customFormat="1" spans="1:10">
       <c r="A67">
-        <f t="shared" si="7"/>
+        <f>C67*100+D67</f>
         <v>101030510</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -3475,14 +3475,14 @@
         <v>10</v>
       </c>
       <c r="E67" t="str">
-        <f t="shared" si="8"/>
+        <f>_xlfn.TEXTJOIN("|",TRUE,G67,K67)</f>
         <v>10000_20020021</v>
       </c>
       <c r="F67">
         <v>99999</v>
       </c>
       <c r="G67" t="str">
-        <f t="shared" si="9"/>
+        <f>_xlfn.TEXTJOIN("_",TRUE,H67:I67)</f>
         <v>10000_20020021</v>
       </c>
       <c r="H67">
